--- a/ROST.xlsx
+++ b/ROST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8894FA02-96F7-40BE-99B4-A16B991E628F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C77212-A149-4085-B228-F354C6ACB597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{32D7F01B-6AE9-4EA4-A41D-85AC8D1A6BED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>Ross Stores</t>
   </si>
@@ -216,7 +216,10 @@
     <t>Store Growth</t>
   </si>
   <si>
-    <t>FQ326</t>
+    <t>FQ426</t>
+  </si>
+  <si>
+    <t>FY26</t>
   </si>
 </sst>
 </file>
@@ -425,7 +428,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -464,6 +467,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -827,7 +831,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>176.36</v>
+        <v>216.48</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -838,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="3">
-        <v>321.27</v>
+        <v>322.35679499999998</v>
       </c>
       <c r="I4" s="27" t="s">
         <v>59</v>
@@ -853,7 +857,7 @@
       </c>
       <c r="H5" s="3">
         <f>H4*H3</f>
-        <v>56659.177199999998</v>
+        <v>69783.79898159999</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -861,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="3">
-        <v>4061.1729999999998</v>
+        <v>4594.3919999999998</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>59</v>
@@ -878,8 +882,8 @@
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <f>1017.54+499.432</f>
-        <v>1516.972</v>
+        <f>1017.863+499.743</f>
+        <v>1517.606</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>59</v>
@@ -901,7 +905,7 @@
       </c>
       <c r="H8" s="3">
         <f>H5-H6+H7</f>
-        <v>54114.976199999997</v>
+        <v>66707.012981599997</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -1026,6 +1030,9 @@
       <c r="V2" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="W2" s="27" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1054,7 +1061,9 @@
       </c>
       <c r="L3" s="19"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
+      <c r="N3" s="19">
+        <v>1904</v>
+      </c>
       <c r="O3" s="19"/>
       <c r="P3" s="19"/>
       <c r="Q3" s="19"/>
@@ -1069,7 +1078,9 @@
       <c r="V3" s="19">
         <v>1831</v>
       </c>
-      <c r="W3" s="20"/>
+      <c r="W3" s="19">
+        <v>1904</v>
+      </c>
       <c r="X3" s="20"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
@@ -1099,7 +1110,9 @@
       </c>
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="N4" s="19">
+        <v>363</v>
+      </c>
       <c r="O4" s="19"/>
       <c r="P4" s="19"/>
       <c r="Q4" s="19"/>
@@ -1114,7 +1127,9 @@
       <c r="V4" s="19">
         <v>355</v>
       </c>
-      <c r="W4" s="20"/>
+      <c r="W4" s="19">
+        <v>363</v>
+      </c>
       <c r="X4" s="20"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -1151,7 +1166,10 @@
       <c r="M5" s="21">
         <v>2273</v>
       </c>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21">
+        <f>+N3+N4</f>
+        <v>2267</v>
+      </c>
       <c r="O5" s="21"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
@@ -1166,7 +1184,10 @@
       <c r="V5" s="22">
         <v>2186</v>
       </c>
-      <c r="W5" s="22"/>
+      <c r="W5" s="21">
+        <f>+W3+W4</f>
+        <v>2267</v>
+      </c>
       <c r="X5" s="22"/>
       <c r="Y5" s="1"/>
     </row>
@@ -1229,7 +1250,10 @@
       <c r="M8" s="23">
         <v>5600.9459999999999</v>
       </c>
-      <c r="N8" s="23"/>
+      <c r="N8" s="23">
+        <f>+W8-SUM(K8:M8)</f>
+        <v>6635.4900000000016</v>
+      </c>
       <c r="O8" s="23"/>
       <c r="P8" s="23">
         <v>14134.732</v>
@@ -1252,6 +1276,9 @@
       <c r="V8" s="23">
         <v>21129.219000000001</v>
       </c>
+      <c r="W8" s="23">
+        <v>22750.559000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
@@ -1291,7 +1318,10 @@
       <c r="M9" s="3">
         <v>4032.4459999999999</v>
       </c>
-      <c r="N9" s="3"/>
+      <c r="N9" s="28">
+        <f>+W9-SUM(K9:M9)</f>
+        <v>4831.2770000000019</v>
+      </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3">
         <v>10042.638000000001</v>
@@ -1314,6 +1344,11 @@
       <c r="V9" s="3">
         <v>15260.505999999999</v>
       </c>
+      <c r="W9" s="3">
+        <v>16447.256000000001</v>
+      </c>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
@@ -1348,7 +1383,7 @@
         <v>1437.0710000000004</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" ref="J10:M10" si="9">J8-J9</f>
+        <f t="shared" ref="J10:N10" si="9">J8-J9</f>
         <v>1568.6570000000029</v>
       </c>
       <c r="K10" s="3">
@@ -1363,7 +1398,10 @@
         <f t="shared" si="9"/>
         <v>1568.5</v>
       </c>
-      <c r="N10" s="3"/>
+      <c r="N10" s="3">
+        <f t="shared" si="9"/>
+        <v>1804.2129999999997</v>
+      </c>
       <c r="O10" s="23"/>
       <c r="P10" s="3">
         <f t="shared" ref="P10:T10" si="10">P8-P9</f>
@@ -1393,6 +1431,12 @@
         <f>V8-V9</f>
         <v>5868.7130000000016</v>
       </c>
+      <c r="W10" s="3">
+        <f>W8-W9</f>
+        <v>6303.3029999999999</v>
+      </c>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
@@ -1432,7 +1476,10 @@
       <c r="M11" s="3">
         <v>920.00199999999995</v>
       </c>
-      <c r="N11" s="3"/>
+      <c r="N11" s="28">
+        <f>+W11-SUM(K11:M11)</f>
+        <v>990.09799999999996</v>
+      </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3">
         <v>2042.6980000000001</v>
@@ -1455,6 +1502,11 @@
       <c r="V11" s="3">
         <v>3283.127</v>
       </c>
+      <c r="W11" s="3">
+        <v>3595.9459999999999</v>
+      </c>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
@@ -1489,7 +1541,7 @@
         <v>604.21600000000035</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:M12" si="18">J10-J11</f>
+        <f t="shared" ref="J12:N12" si="18">J10-J11</f>
         <v>731.02400000000307</v>
       </c>
       <c r="K12" s="3">
@@ -1504,7 +1556,10 @@
         <f t="shared" si="18"/>
         <v>648.49800000000005</v>
       </c>
-      <c r="N12" s="3"/>
+      <c r="N12" s="3">
+        <f t="shared" si="18"/>
+        <v>814.11499999999978</v>
+      </c>
       <c r="O12" s="23"/>
       <c r="P12" s="3">
         <f t="shared" ref="P12:T12" si="19">P10-P11</f>
@@ -1534,6 +1589,12 @@
         <f>V10-V11</f>
         <v>2585.5860000000016</v>
       </c>
+      <c r="W12" s="3">
+        <f>W10-W11</f>
+        <v>2707.357</v>
+      </c>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
@@ -1573,7 +1634,10 @@
       <c r="M13" s="3">
         <v>33.9</v>
       </c>
-      <c r="N13" s="3"/>
+      <c r="N13" s="28">
+        <f>+W13-SUM(K13:M13)</f>
+        <v>34.14500000000001</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3">
         <v>-7.6760000000000002</v>
@@ -1596,6 +1660,11 @@
       <c r="V13" s="3">
         <v>171.56800000000001</v>
       </c>
+      <c r="W13" s="3">
+        <v>134.80000000000001</v>
+      </c>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
@@ -1630,7 +1699,7 @@
         <v>646.74300000000039</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" ref="J14:M14" si="27">J12+J13</f>
+        <f t="shared" ref="J14:N14" si="27">J12+J13</f>
         <v>770.75600000000304</v>
       </c>
       <c r="K14" s="3">
@@ -1645,7 +1714,10 @@
         <f t="shared" si="27"/>
         <v>682.39800000000002</v>
       </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="3">
+        <f t="shared" si="27"/>
+        <v>848.25999999999976</v>
+      </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3">
         <f t="shared" ref="P14:T14" si="28">P12+P13</f>
@@ -1675,6 +1747,12 @@
         <f>V12+V13</f>
         <v>2757.1540000000018</v>
       </c>
+      <c r="W14" s="3">
+        <f>W12+W13</f>
+        <v>2842.1570000000002</v>
+      </c>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
@@ -1714,7 +1792,10 @@
       <c r="M15" s="3">
         <v>170.46299999999999</v>
       </c>
-      <c r="N15" s="3"/>
+      <c r="N15" s="28">
+        <f>+W15-SUM(K15:M15)</f>
+        <v>202.3950000000001</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3">
         <v>677.96699999999998</v>
@@ -1737,6 +1818,11 @@
       <c r="V15" s="3">
         <v>666.42399999999998</v>
       </c>
+      <c r="W15" s="3">
+        <v>697.11300000000006</v>
+      </c>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
@@ -1771,7 +1857,7 @@
         <v>488.80800000000039</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" ref="J16:M16" si="36">J14-J15</f>
+        <f t="shared" ref="J16:N16" si="36">J14-J15</f>
         <v>586.77500000000305</v>
       </c>
       <c r="K16" s="3">
@@ -1786,7 +1872,10 @@
         <f t="shared" si="36"/>
         <v>511.93500000000006</v>
       </c>
-      <c r="N16" s="3"/>
+      <c r="N16" s="3">
+        <f t="shared" si="36"/>
+        <v>645.86499999999967</v>
+      </c>
       <c r="O16" s="23"/>
       <c r="P16" s="3">
         <f t="shared" ref="P16:T16" si="37">P14-P15</f>
@@ -1816,8 +1905,14 @@
         <f>V14-V15</f>
         <v>2090.7300000000018</v>
       </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3">
+        <f>W14-W15</f>
+        <v>2145.0439999999999</v>
+      </c>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1838,12 +1933,12 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="24">
-        <f t="shared" ref="C18:M18" si="38">C16/C19</f>
+        <f t="shared" ref="C18:N18" si="38">C16/C19</f>
         <v>1.100997192714664</v>
       </c>
       <c r="D18" s="24">
@@ -1886,7 +1981,10 @@
         <f t="shared" si="38"/>
         <v>1.5934727799047532</v>
       </c>
-      <c r="N18" s="24"/>
+      <c r="N18" s="24">
+        <f t="shared" si="38"/>
+        <v>2.0045468653010543</v>
+      </c>
       <c r="O18" s="24"/>
       <c r="P18" s="24">
         <f t="shared" ref="P18:V18" si="39">P16/P19</f>
@@ -1916,8 +2014,12 @@
         <f t="shared" si="39"/>
         <v>6.3626735809953399</v>
       </c>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="24">
+        <f t="shared" ref="W18" si="40">W16/W19</f>
+        <v>6.657079014338029</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -1955,7 +2057,9 @@
       <c r="M19" s="3">
         <v>321.27</v>
       </c>
-      <c r="N19" s="3"/>
+      <c r="N19" s="3">
+        <v>322.2</v>
+      </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3">
         <v>381.17399999999998</v>
@@ -1978,8 +2082,11 @@
       <c r="V19" s="3">
         <v>328.59300000000002</v>
       </c>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3">
+        <v>322.22000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -2000,7 +2107,7 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>58</v>
       </c>
@@ -2009,19 +2116,19 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="25" t="e">
-        <f t="shared" ref="G21:J21" si="40">+G5/C5-1</f>
+        <f t="shared" ref="G21:J21" si="41">+G5/C5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H21" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4.2212518195051008E-2</v>
       </c>
       <c r="I21" s="25" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J21" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.6510194404931307E-2</v>
       </c>
       <c r="K21" s="25" t="e">
@@ -2029,23 +2136,37 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L21" s="25">
-        <f t="shared" ref="L21:M21" si="41">+L5/H5-1</f>
+        <f t="shared" ref="L21:N21" si="42">+L5/H5-1</f>
         <v>3.9571694599627616E-2</v>
       </c>
       <c r="M21" s="25">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.6952554744525523E-2</v>
       </c>
-      <c r="N21" s="3"/>
+      <c r="N21" s="25">
+        <f t="shared" si="42"/>
+        <v>3.7053979871912279E-2</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U21" s="25">
+        <f>+U5/T5-1</f>
+        <v>4.6650124069478993E-2</v>
+      </c>
+      <c r="V21" s="25">
+        <f>+V5/U5-1</f>
+        <v>3.6510194404931307E-2</v>
+      </c>
+      <c r="W21" s="25">
+        <f>+W5/V5-1</f>
+        <v>3.7053979871912279E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
@@ -2058,46 +2179,49 @@
         <v>8.084680442638259E-2</v>
       </c>
       <c r="H22" s="26">
-        <f t="shared" ref="H22:M22" si="42">H8/D8-1</f>
+        <f t="shared" ref="H22:N22" si="43">H8/D8-1</f>
         <v>7.1453047221780475E-2</v>
       </c>
       <c r="I22" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.9748120196172456E-2</v>
       </c>
       <c r="J22" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.19805325533115692</v>
       </c>
       <c r="K22" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.6122323961361493E-2</v>
       </c>
       <c r="L22" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>4.5698748316554516E-2</v>
       </c>
       <c r="M22" s="26">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.1044281270840095</v>
       </c>
-      <c r="N22" s="26"/>
+      <c r="N22" s="26">
+        <f t="shared" si="43"/>
+        <v>0.12232355746405044</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="23"/>
       <c r="Q22" s="26">
-        <f t="shared" ref="Q22:T22" si="43">Q8/P8-1</f>
+        <f t="shared" ref="Q22:T22" si="44">Q8/P8-1</f>
         <v>6.0051297753646704E-2</v>
       </c>
       <c r="R22" s="26">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>7.0446098155302561E-2</v>
       </c>
       <c r="S22" s="26">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.17938511783068756</v>
       </c>
       <c r="T22" s="26">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-1.1652154624353428E-2</v>
       </c>
       <c r="U22" s="26">
@@ -2108,75 +2232,82 @@
         <f>V8/U8-1</f>
         <v>3.691810267301654E-2</v>
       </c>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="26">
+        <f>W8/V8-1</f>
+        <v>7.6734497380144484E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C23" s="25">
-        <f t="shared" ref="C23:J23" si="44">C10/C8</f>
+        <f t="shared" ref="C23:J23" si="45">C10/C8</f>
         <v>0.26744471137694592</v>
       </c>
       <c r="D23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.27671008864405688</v>
       </c>
       <c r="E23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.27626857188920922</v>
       </c>
       <c r="F23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.27671008864405688</v>
       </c>
       <c r="G23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.2814689463936994</v>
       </c>
       <c r="H23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.28285288431114858</v>
       </c>
       <c r="I23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.283370279416503</v>
       </c>
       <c r="J23" s="25">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.26532188349027547</v>
       </c>
       <c r="K23" s="25">
-        <f t="shared" ref="K23:L23" si="45">K10/K8</f>
+        <f t="shared" ref="K23:L23" si="46">K10/K8</f>
         <v>0.28156733509583098</v>
       </c>
       <c r="L23" s="25">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.27616983580845672</v>
       </c>
       <c r="M23" s="25">
-        <f t="shared" ref="M23" si="46">M10/M8</f>
+        <f t="shared" ref="M23:N23" si="47">M10/M8</f>
         <v>0.28004197862289693</v>
       </c>
-      <c r="N23" s="25"/>
+      <c r="N23" s="25">
+        <f t="shared" si="47"/>
+        <v>0.27190350674931307</v>
+      </c>
       <c r="O23" s="3"/>
       <c r="P23" s="25">
-        <f t="shared" ref="P23:T23" si="47">P10/P8</f>
+        <f t="shared" ref="P23:T23" si="48">P10/P8</f>
         <v>0.28950630263099431</v>
       </c>
       <c r="Q23" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.28412936568198394</v>
       </c>
       <c r="R23" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.28074477870385656</v>
       </c>
       <c r="S23" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.27528387770849222</v>
       </c>
       <c r="T23" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.25404591580293134</v>
       </c>
       <c r="U23" s="25">
@@ -2187,75 +2318,82 @@
         <f>V10/V8</f>
         <v>0.27775342761130933</v>
       </c>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="25">
+        <f>W10/W8</f>
+        <v>0.2770614559404892</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="25">
-        <f t="shared" ref="C24:J24" si="48">C12/C8</f>
+        <f t="shared" ref="C24:J24" si="49">C12/C8</f>
         <v>0.1014215453537799</v>
       </c>
       <c r="D24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11299913574830713</v>
       </c>
       <c r="E24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11170108971868987</v>
       </c>
       <c r="F24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11299913574830713</v>
       </c>
       <c r="G24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.1216765845345484</v>
       </c>
       <c r="H24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.124677187921216</v>
       </c>
       <c r="I24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11914293500315701</v>
       </c>
       <c r="J24" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.12364504449130408</v>
       </c>
       <c r="K24" s="25">
-        <f t="shared" ref="K24:L24" si="49">K12/K8</f>
+        <f t="shared" ref="K24:L24" si="50">K12/K8</f>
         <v>0.12165968468021171</v>
       </c>
       <c r="L24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.11543795504265394</v>
       </c>
       <c r="M24" s="25">
-        <f t="shared" ref="M24" si="50">M12/M8</f>
+        <f t="shared" ref="M24:N24" si="51">M12/M8</f>
         <v>0.11578365511826039</v>
       </c>
-      <c r="N24" s="25"/>
+      <c r="N24" s="25">
+        <f t="shared" si="51"/>
+        <v>0.12269101452944689</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="25">
-        <f t="shared" ref="P24:T24" si="51">P12/P8</f>
+        <f t="shared" ref="P24:T24" si="52">P12/P8</f>
         <v>0.14499008541513195</v>
       </c>
       <c r="Q24" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.13619704447700307</v>
       </c>
       <c r="R24" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.13380960358494534</v>
       </c>
       <c r="S24" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.12332617405442643</v>
       </c>
       <c r="T24" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.10645855821638087</v>
       </c>
       <c r="U24" s="25">
@@ -2266,75 +2404,82 @@
         <f>V12/V8</f>
         <v>0.12237016427346423</v>
       </c>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="25">
+        <f>W12/W8</f>
+        <v>0.1190017792529845</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="25">
-        <f t="shared" ref="C25:J25" si="52">C16/C8</f>
+        <f t="shared" ref="C25:J25" si="53">C16/C8</f>
         <v>8.2806896855531067E-2</v>
       </c>
       <c r="D25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.0441254694872478E-2</v>
       </c>
       <c r="E25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.0830602115922754E-2</v>
       </c>
       <c r="F25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.0441254694872478E-2</v>
       </c>
       <c r="G25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.10044941743290078</v>
       </c>
       <c r="H25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.9698365150082693E-2</v>
       </c>
       <c r="I25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.6386093339175374E-2</v>
       </c>
       <c r="J25" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.924683865561873E-2</v>
       </c>
       <c r="K25" s="25">
-        <f t="shared" ref="K25:L25" si="53">K16/K8</f>
+        <f t="shared" ref="K25:L25" si="54">K16/K8</f>
         <v>9.6138773926668697E-2</v>
       </c>
       <c r="L25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>9.1875752375771211E-2</v>
       </c>
       <c r="M25" s="25">
-        <f t="shared" ref="M25" si="54">M16/M8</f>
+        <f t="shared" ref="M25:N25" si="55">M16/M8</f>
         <v>9.1401523956845879E-2</v>
       </c>
-      <c r="N25" s="25"/>
+      <c r="N25" s="25">
+        <f t="shared" si="55"/>
+        <v>9.7334936832095223E-2</v>
+      </c>
       <c r="O25" s="3"/>
       <c r="P25" s="25">
-        <f t="shared" ref="P25:T25" si="55">P16/P8</f>
+        <f t="shared" ref="P25:T25" si="56">P16/P8</f>
         <v>9.6482409429481844E-2</v>
       </c>
       <c r="Q25" s="25">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.10594671846928568</v>
       </c>
       <c r="R25" s="25">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.1035551119444372</v>
       </c>
       <c r="S25" s="25">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>9.1064008267180294E-2</v>
       </c>
       <c r="T25" s="25">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>8.0875846692864059E-2</v>
       </c>
       <c r="U25" s="25">
@@ -2345,75 +2490,82 @@
         <f>V16/V8</f>
         <v>9.894970561855608E-2</v>
       </c>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="25">
+        <f>W16/W8</f>
+        <v>9.4285331626356952E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="25">
-        <f t="shared" ref="C26:J26" si="56">C15/C14</f>
+        <f t="shared" ref="C26:J26" si="57">C15/C14</f>
         <v>0.23614739715344146</v>
       </c>
       <c r="D26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24969992636848723</v>
       </c>
       <c r="E26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24620089985339466</v>
       </c>
       <c r="F26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24969992636848723</v>
       </c>
       <c r="G26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.23400040498349459</v>
       </c>
       <c r="H26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24969683685552918</v>
       </c>
       <c r="I26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24420055570759933</v>
       </c>
       <c r="J26" s="25">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.23870200167108555</v>
       </c>
       <c r="K26" s="25">
-        <f t="shared" ref="K26:L26" si="57">K15/K14</f>
+        <f t="shared" ref="K26:L26" si="58">K15/K14</f>
         <v>0.25220049338486689</v>
       </c>
       <c r="L26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.24249947809489722</v>
       </c>
       <c r="M26" s="25">
-        <f t="shared" ref="M26" si="58">M15/M14</f>
+        <f t="shared" ref="M26:N26" si="59">M15/M14</f>
         <v>0.24979997010542232</v>
       </c>
-      <c r="N26" s="25"/>
+      <c r="N26" s="25">
+        <f t="shared" si="59"/>
+        <v>0.23860019333694876</v>
+      </c>
       <c r="O26" s="3"/>
       <c r="P26" s="25">
-        <f t="shared" ref="P26:T26" si="59">P15/P14</f>
+        <f t="shared" ref="P26:T26" si="60">P15/P14</f>
         <v>0.33205679525106302</v>
       </c>
       <c r="Q26" s="25">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.22596149157725784</v>
       </c>
       <c r="R26" s="25">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.2325753319336428</v>
       </c>
       <c r="S26" s="25">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.23729976002196115</v>
       </c>
       <c r="T26" s="25">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.23922044348421528</v>
       </c>
       <c r="U26" s="25">
@@ -2424,8 +2576,12 @@
         <f>V15/V14</f>
         <v>0.24170720968070683</v>
       </c>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="25">
+        <f>W15/W14</f>
+        <v>0.24527603506773202</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2446,7 +2602,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2467,7 +2623,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2488,7 +2644,7 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -2509,7 +2665,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2530,7 +2686,7 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>

--- a/ROST.xlsx
+++ b/ROST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C77212-A149-4085-B228-F354C6ACB597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EAFA02-B3AB-4677-BB19-46155A20020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{32D7F01B-6AE9-4EA4-A41D-85AC8D1A6BED}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>Ross Stores</t>
   </si>
@@ -216,10 +216,22 @@
     <t>Store Growth</t>
   </si>
   <si>
-    <t>FQ426</t>
+    <t>FY26</t>
   </si>
   <si>
-    <t>FY26</t>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
+  </si>
+  <si>
+    <t>FQ127</t>
   </si>
 </sst>
 </file>
@@ -231,13 +243,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -425,49 +443,52 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -831,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>216.48</v>
+        <v>232.02</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -842,10 +863,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="3">
-        <v>322.35679499999998</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>59</v>
+        <v>319.95699999999999</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -857,7 +878,7 @@
       </c>
       <c r="H5" s="3">
         <f>H4*H3</f>
-        <v>69783.79898159999</v>
+        <v>74236.423139999999</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -865,10 +886,10 @@
         <v>4</v>
       </c>
       <c r="H6" s="3">
-        <v>4594.3919999999998</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>59</v>
+        <v>4130.9799999999996</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -882,11 +903,11 @@
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <f>1017.863+499.743</f>
-        <v>1517.606</v>
-      </c>
-      <c r="I7" s="27" t="s">
-        <v>59</v>
+        <f>776.843+241.344</f>
+        <v>1018.1869999999999</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -905,7 +926,7 @@
       </c>
       <c r="H8" s="3">
         <f>H5-H6+H7</f>
-        <v>66707.012981599997</v>
+        <v>71123.630140000008</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -958,7 +979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D02FF4-0653-4938-9B83-B4E1E02AD4C6}">
-  <dimension ref="A1:Y486"/>
+  <dimension ref="A1:AC486"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -966,12 +987,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
@@ -1008,33 +1029,45 @@
       <c r="N2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="W2" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA2" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>46</v>
       </c>
@@ -1044,7 +1077,7 @@
       </c>
       <c r="E3" s="19"/>
       <c r="F3" s="19">
-        <f>+U3</f>
+        <f>+Y3</f>
         <v>1764</v>
       </c>
       <c r="G3" s="19"/>
@@ -1053,7 +1086,7 @@
       </c>
       <c r="I3" s="19"/>
       <c r="J3" s="19">
-        <f>+V3</f>
+        <f>+Z3</f>
         <v>1831</v>
       </c>
       <c r="K3" s="19">
@@ -1069,21 +1102,25 @@
       <c r="Q3" s="19"/>
       <c r="R3" s="19"/>
       <c r="S3" s="19"/>
-      <c r="T3" s="19">
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19">
         <v>1693</v>
       </c>
-      <c r="U3" s="19">
+      <c r="Y3" s="19">
         <v>1764</v>
       </c>
-      <c r="V3" s="19">
+      <c r="Z3" s="19">
         <v>1831</v>
       </c>
-      <c r="W3" s="19">
+      <c r="AA3" s="19">
         <v>1904</v>
       </c>
-      <c r="X3" s="20"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB3" s="20"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>48</v>
       </c>
@@ -1093,7 +1130,7 @@
       </c>
       <c r="E4" s="19"/>
       <c r="F4" s="19">
-        <f t="shared" ref="F4:F5" si="0">+U4</f>
+        <f t="shared" ref="F4:F5" si="0">+Y4</f>
         <v>345</v>
       </c>
       <c r="G4" s="19"/>
@@ -1102,7 +1139,7 @@
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19">
-        <f t="shared" ref="J4:J5" si="1">+V4</f>
+        <f t="shared" ref="J4:J5" si="1">+Z4</f>
         <v>355</v>
       </c>
       <c r="K4" s="19">
@@ -1118,21 +1155,25 @@
       <c r="Q4" s="19"/>
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
-      <c r="T4" s="19">
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19">
         <v>322</v>
       </c>
-      <c r="U4" s="19">
+      <c r="Y4" s="19">
         <v>345</v>
       </c>
-      <c r="V4" s="19">
+      <c r="Z4" s="19">
         <v>355</v>
       </c>
-      <c r="W4" s="19">
+      <c r="AA4" s="19">
         <v>363</v>
       </c>
-      <c r="X4" s="20"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB4" s="20"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>47</v>
       </c>
@@ -1170,28 +1211,34 @@
         <f>+N3+N4</f>
         <v>2267</v>
       </c>
-      <c r="O5" s="21"/>
+      <c r="O5" s="21">
+        <v>2282</v>
+      </c>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
       <c r="R5" s="21"/>
       <c r="S5" s="21"/>
-      <c r="T5" s="21">
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21">
         <v>2015</v>
       </c>
-      <c r="U5" s="21">
+      <c r="Y5" s="21">
         <v>2109</v>
       </c>
-      <c r="V5" s="22">
+      <c r="Z5" s="22">
         <v>2186</v>
       </c>
-      <c r="W5" s="21">
-        <f>+W3+W4</f>
+      <c r="AA5" s="21">
+        <f>+AA3+AA4</f>
         <v>2267</v>
       </c>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="1"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB5" s="22"/>
+      <c r="AC5" s="1"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1211,8 +1258,12 @@
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1238,7 +1289,7 @@
         <v>5071.3540000000003</v>
       </c>
       <c r="J8" s="23">
-        <f>+V8-SUM(G8:I8)</f>
+        <f>+Z8-SUM(G8:I8)</f>
         <v>5912.2790000000023</v>
       </c>
       <c r="K8" s="23">
@@ -1251,36 +1302,42 @@
         <v>5600.9459999999999</v>
       </c>
       <c r="N8" s="23">
-        <f>+W8-SUM(K8:M8)</f>
+        <f>+AA8-SUM(K8:M8)</f>
         <v>6635.4900000000016</v>
       </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23">
+      <c r="O8" s="23">
+        <v>6010.4759999999997</v>
+      </c>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23">
         <v>14134.732</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="U8" s="23">
         <v>14983.540999999999</v>
       </c>
-      <c r="R8" s="23">
+      <c r="V8" s="23">
         <v>16039.073</v>
       </c>
-      <c r="S8" s="23">
+      <c r="W8" s="23">
         <v>18916.243999999999</v>
       </c>
-      <c r="T8" s="23">
+      <c r="X8" s="23">
         <v>18695.829000000002</v>
       </c>
-      <c r="U8" s="23">
+      <c r="Y8" s="23">
         <v>20376.940999999999</v>
       </c>
-      <c r="V8" s="23">
+      <c r="Z8" s="23">
         <v>21129.219000000001</v>
       </c>
-      <c r="W8" s="23">
+      <c r="AA8" s="23">
         <v>22750.559000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1306,7 +1363,7 @@
         <v>3634.2829999999999</v>
       </c>
       <c r="J9" s="3">
-        <f>+V9-SUM(G9:I9)</f>
+        <f>+Z9-SUM(G9:I9)</f>
         <v>4343.6219999999994</v>
       </c>
       <c r="K9" s="3">
@@ -1319,38 +1376,44 @@
         <v>4032.4459999999999</v>
       </c>
       <c r="N9" s="28">
-        <f>+W9-SUM(K9:M9)</f>
+        <f>+AA9-SUM(K9:M9)</f>
         <v>4831.2770000000019</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3">
+      <c r="O9" s="28">
+        <v>4230.5889999999999</v>
+      </c>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3">
         <v>10042.638000000001</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>10726.277</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>11536.187</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>13708.906999999999</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>13946.23</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>14801.601000000001</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>15260.505999999999</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>16447.256000000001</v>
       </c>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1383,7 +1446,7 @@
         <v>1437.0710000000004</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" ref="J10:N10" si="9">J8-J9</f>
+        <f t="shared" ref="J10:O10" si="9">J8-J9</f>
         <v>1568.6570000000029</v>
       </c>
       <c r="K10" s="3">
@@ -1402,43 +1465,50 @@
         <f t="shared" si="9"/>
         <v>1804.2129999999997</v>
       </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="3">
-        <f t="shared" ref="P10:T10" si="10">P8-P9</f>
+      <c r="O10" s="3">
+        <f t="shared" si="9"/>
+        <v>1779.8869999999997</v>
+      </c>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="3">
+        <f t="shared" ref="T10:X10" si="10">T8-T9</f>
         <v>4092.0939999999991</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <f t="shared" si="10"/>
         <v>4257.2639999999992</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <f t="shared" si="10"/>
         <v>4502.8860000000004</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <f t="shared" si="10"/>
         <v>5207.3369999999995</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <f t="shared" si="10"/>
         <v>4749.599000000002</v>
       </c>
-      <c r="U10" s="3">
-        <f>U8-U9</f>
+      <c r="Y10" s="3">
+        <f>Y8-Y9</f>
         <v>5575.3399999999983</v>
       </c>
-      <c r="V10" s="3">
-        <f>V8-V9</f>
+      <c r="Z10" s="3">
+        <f>Z8-Z9</f>
         <v>5868.7130000000016</v>
       </c>
-      <c r="W10" s="3">
-        <f>W8-W9</f>
+      <c r="AA10" s="3">
+        <f>AA8-AA9</f>
         <v>6303.3029999999999</v>
       </c>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1464,7 +1534,7 @@
         <v>832.85500000000002</v>
       </c>
       <c r="J11" s="3">
-        <f>+V11-SUM(G11:I11)</f>
+        <f>+Z11-SUM(G11:I11)</f>
         <v>837.63299999999981</v>
       </c>
       <c r="K11" s="3">
@@ -1477,38 +1547,44 @@
         <v>920.00199999999995</v>
       </c>
       <c r="N11" s="28">
-        <f>+W11-SUM(K11:M11)</f>
+        <f>+AA11-SUM(K11:M11)</f>
         <v>990.09799999999996</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3">
+      <c r="O11" s="28">
+        <v>975.86099999999999</v>
+      </c>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3">
         <v>2042.6980000000001</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="U11" s="3">
         <v>2216.5500000000002</v>
       </c>
-      <c r="R11" s="3">
+      <c r="V11" s="3">
         <v>2356.7040000000002</v>
       </c>
-      <c r="S11" s="3">
+      <c r="W11" s="3">
         <v>2874.4690000000001</v>
       </c>
-      <c r="T11" s="3">
+      <c r="X11" s="3">
         <v>2759.268</v>
       </c>
-      <c r="U11" s="3">
+      <c r="Y11" s="3">
         <v>3267.6770000000001</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <v>3283.127</v>
       </c>
-      <c r="W11" s="3">
+      <c r="AA11" s="3">
         <v>3595.9459999999999</v>
       </c>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1541,7 +1617,7 @@
         <v>604.21600000000035</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:N12" si="18">J10-J11</f>
+        <f t="shared" ref="J12:O12" si="18">J10-J11</f>
         <v>731.02400000000307</v>
       </c>
       <c r="K12" s="3">
@@ -1560,43 +1636,50 @@
         <f t="shared" si="18"/>
         <v>814.11499999999978</v>
       </c>
-      <c r="O12" s="23"/>
-      <c r="P12" s="3">
-        <f t="shared" ref="P12:T12" si="19">P10-P11</f>
+      <c r="O12" s="3">
+        <f t="shared" si="18"/>
+        <v>804.02599999999973</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="3">
+        <f t="shared" ref="T12:X12" si="19">T10-T11</f>
         <v>2049.3959999999988</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <f t="shared" si="19"/>
         <v>2040.713999999999</v>
       </c>
-      <c r="R12" s="3">
+      <c r="V12" s="3">
         <f t="shared" si="19"/>
         <v>2146.1820000000002</v>
       </c>
-      <c r="S12" s="3">
+      <c r="W12" s="3">
         <f t="shared" si="19"/>
         <v>2332.8679999999995</v>
       </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
         <f t="shared" si="19"/>
         <v>1990.3310000000019</v>
       </c>
-      <c r="U12" s="3">
-        <f>U10-U11</f>
+      <c r="Y12" s="3">
+        <f>Y10-Y11</f>
         <v>2307.6629999999982</v>
       </c>
-      <c r="V12" s="3">
-        <f>V10-V11</f>
+      <c r="Z12" s="3">
+        <f>Z10-Z11</f>
         <v>2585.5860000000016</v>
       </c>
-      <c r="W12" s="3">
-        <f>W10-W11</f>
+      <c r="AA12" s="3">
+        <f>AA10-AA11</f>
         <v>2707.357</v>
       </c>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1622,7 +1705,7 @@
         <v>42.527000000000001</v>
       </c>
       <c r="J13" s="3">
-        <f>+V13-SUM(G13:I13)</f>
+        <f>+Z13-SUM(G13:I13)</f>
         <v>39.731999999999999</v>
       </c>
       <c r="K13" s="3">
@@ -1635,38 +1718,44 @@
         <v>33.9</v>
       </c>
       <c r="N13" s="28">
-        <f>+W13-SUM(K13:M13)</f>
+        <f>+AA13-SUM(K13:M13)</f>
         <v>34.14500000000001</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3">
+      <c r="O13" s="28">
+        <v>33.448999999999998</v>
+      </c>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3">
         <v>-7.6760000000000002</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="U13" s="3">
         <v>10.162000000000001</v>
       </c>
-      <c r="R13" s="3">
+      <c r="V13" s="3">
         <v>18.106000000000002</v>
       </c>
-      <c r="S13" s="3">
+      <c r="W13" s="3">
         <v>-74.328000000000003</v>
       </c>
-      <c r="T13" s="3">
+      <c r="X13" s="3">
         <v>-2.8420000000000001</v>
       </c>
-      <c r="U13" s="3">
+      <c r="Y13" s="3">
         <v>164.11799999999999</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>171.56800000000001</v>
       </c>
-      <c r="W13" s="3">
+      <c r="AA13" s="3">
         <v>134.80000000000001</v>
       </c>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1699,7 +1788,7 @@
         <v>646.74300000000039</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" ref="J14:N14" si="27">J12+J13</f>
+        <f t="shared" ref="J14:O14" si="27">J12+J13</f>
         <v>770.75600000000304</v>
       </c>
       <c r="K14" s="3">
@@ -1718,43 +1807,50 @@
         <f t="shared" si="27"/>
         <v>848.25999999999976</v>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3">
-        <f t="shared" ref="P14:T14" si="28">P12+P13</f>
+      <c r="O14" s="3">
+        <f t="shared" si="27"/>
+        <v>837.47499999999968</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3">
+        <f t="shared" ref="T14:X14" si="28">T12+T13</f>
         <v>2041.7199999999989</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <f t="shared" si="28"/>
         <v>2050.8759999999988</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <f t="shared" si="28"/>
         <v>2164.2880000000005</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <f t="shared" si="28"/>
         <v>2258.5399999999995</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <f t="shared" si="28"/>
         <v>1987.4890000000019</v>
       </c>
-      <c r="U14" s="3">
-        <f>U12+U13</f>
+      <c r="Y14" s="3">
+        <f>Y12+Y13</f>
         <v>2471.7809999999981</v>
       </c>
-      <c r="V14" s="3">
-        <f>V12+V13</f>
+      <c r="Z14" s="3">
+        <f>Z12+Z13</f>
         <v>2757.1540000000018</v>
       </c>
-      <c r="W14" s="3">
-        <f>W12+W13</f>
+      <c r="AA14" s="3">
+        <f>AA12+AA13</f>
         <v>2842.1570000000002</v>
       </c>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1780,7 +1876,7 @@
         <v>157.935</v>
       </c>
       <c r="J15" s="3">
-        <f>+V15-SUM(G15:I15)</f>
+        <f>+Z15-SUM(G15:I15)</f>
         <v>183.98099999999994</v>
       </c>
       <c r="K15" s="3">
@@ -1793,38 +1889,44 @@
         <v>170.46299999999999</v>
       </c>
       <c r="N15" s="28">
-        <f>+W15-SUM(K15:M15)</f>
+        <f>+AA15-SUM(K15:M15)</f>
         <v>202.3950000000001</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3">
+      <c r="O15" s="28">
+        <v>187.511</v>
+      </c>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3">
         <v>677.96699999999998</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="U15" s="3">
         <v>463.41899999999998</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <v>503.36</v>
       </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
         <v>535.95100000000002</v>
       </c>
-      <c r="T15" s="3">
+      <c r="X15" s="3">
         <v>475.44799999999998</v>
       </c>
-      <c r="U15" s="3">
+      <c r="Y15" s="3">
         <v>597.26099999999997</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>666.42399999999998</v>
       </c>
-      <c r="W15" s="3">
+      <c r="AA15" s="3">
         <v>697.11300000000006</v>
       </c>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1857,7 +1959,7 @@
         <v>488.80800000000039</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" ref="J16:N16" si="36">J14-J15</f>
+        <f t="shared" ref="J16:O16" si="36">J14-J15</f>
         <v>586.77500000000305</v>
       </c>
       <c r="K16" s="3">
@@ -1876,43 +1978,50 @@
         <f t="shared" si="36"/>
         <v>645.86499999999967</v>
       </c>
-      <c r="O16" s="23"/>
-      <c r="P16" s="3">
-        <f t="shared" ref="P16:T16" si="37">P14-P15</f>
+      <c r="O16" s="3">
+        <f t="shared" si="36"/>
+        <v>649.96399999999971</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="3">
+        <f t="shared" ref="T16:X16" si="37">T14-T15</f>
         <v>1363.7529999999988</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="U16" s="3">
         <f t="shared" si="37"/>
         <v>1587.456999999999</v>
       </c>
-      <c r="R16" s="3">
+      <c r="V16" s="3">
         <f t="shared" si="37"/>
         <v>1660.9280000000003</v>
       </c>
-      <c r="S16" s="3">
+      <c r="W16" s="3">
         <f t="shared" si="37"/>
         <v>1722.5889999999995</v>
       </c>
-      <c r="T16" s="3">
+      <c r="X16" s="3">
         <f t="shared" si="37"/>
         <v>1512.041000000002</v>
       </c>
-      <c r="U16" s="3">
-        <f>U14-U15</f>
+      <c r="Y16" s="3">
+        <f>Y14-Y15</f>
         <v>1874.5199999999982</v>
       </c>
-      <c r="V16" s="3">
-        <f>V14-V15</f>
+      <c r="Z16" s="3">
+        <f>Z14-Z15</f>
         <v>2090.7300000000018</v>
       </c>
-      <c r="W16" s="3">
-        <f>W14-W15</f>
+      <c r="AA16" s="3">
+        <f>AA14-AA15</f>
         <v>2145.0439999999999</v>
       </c>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1932,13 +2041,17 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+    </row>
+    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="24">
-        <f t="shared" ref="C18:N18" si="38">C16/C19</f>
+        <f t="shared" ref="C18:O18" si="38">C16/C19</f>
         <v>1.100997192714664</v>
       </c>
       <c r="D18" s="24">
@@ -1985,41 +2098,48 @@
         <f t="shared" si="38"/>
         <v>2.0045468653010543</v>
       </c>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24">
-        <f t="shared" ref="P18:V18" si="39">P16/P19</f>
+      <c r="O18" s="24">
+        <f t="shared" si="38"/>
+        <v>2.0314104707820104</v>
+      </c>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24">
+        <f t="shared" ref="T18:Z18" si="39">T16/T19</f>
         <v>3.5777702571528982</v>
       </c>
-      <c r="Q18" s="24">
+      <c r="U18" s="24">
         <f t="shared" si="39"/>
         <v>4.2958463790784558</v>
       </c>
-      <c r="R18" s="24">
+      <c r="V18" s="24">
         <f t="shared" si="39"/>
         <v>4.6334841628959289</v>
       </c>
-      <c r="S18" s="24">
+      <c r="W18" s="24">
         <f t="shared" si="39"/>
         <v>4.900735712497438</v>
       </c>
-      <c r="T18" s="24">
+      <c r="X18" s="24">
         <f t="shared" si="39"/>
         <v>4.4024812783154621</v>
       </c>
-      <c r="U18" s="24">
+      <c r="Y18" s="24">
         <f t="shared" si="39"/>
         <v>5.5924603281153447</v>
       </c>
-      <c r="V18" s="24">
+      <c r="Z18" s="24">
         <f t="shared" si="39"/>
         <v>6.3626735809953399</v>
       </c>
-      <c r="W18" s="24">
-        <f t="shared" ref="W18" si="40">W16/W19</f>
+      <c r="AA18" s="24">
+        <f t="shared" ref="AA18" si="40">AA16/AA19</f>
         <v>6.657079014338029</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -2045,7 +2165,7 @@
         <v>327.71</v>
       </c>
       <c r="J19" s="3">
-        <f>+V19</f>
+        <f>+Z19</f>
         <v>328.59300000000002</v>
       </c>
       <c r="K19" s="3">
@@ -2060,33 +2180,39 @@
       <c r="N19" s="3">
         <v>322.2</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3">
+      <c r="O19" s="3">
+        <v>319.95699999999999</v>
+      </c>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3">
         <v>381.17399999999998</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="U19" s="3">
         <v>369.53300000000002</v>
       </c>
-      <c r="R19" s="3">
+      <c r="V19" s="3">
         <v>358.46199999999999</v>
       </c>
-      <c r="S19" s="3">
+      <c r="W19" s="3">
         <v>351.49599999999998</v>
       </c>
-      <c r="T19" s="3">
+      <c r="X19" s="3">
         <v>343.452</v>
       </c>
-      <c r="U19" s="3">
+      <c r="Y19" s="3">
         <v>335.18700000000001</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Z19" s="3">
         <v>328.59300000000002</v>
       </c>
-      <c r="W19" s="3">
+      <c r="AA19" s="3">
         <v>322.22000000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -2106,8 +2232,12 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
-    </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>58</v>
       </c>
@@ -2136,7 +2266,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L21" s="25">
-        <f t="shared" ref="L21:N21" si="42">+L5/H5-1</f>
+        <f t="shared" ref="L21:O21" si="42">+L5/H5-1</f>
         <v>3.9571694599627616E-2</v>
       </c>
       <c r="M21" s="25">
@@ -2147,26 +2277,33 @@
         <f t="shared" si="42"/>
         <v>3.7053979871912279E-2</v>
       </c>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
+      <c r="O21" s="25">
+        <f t="shared" si="42"/>
+        <v>3.4920634920635019E-2</v>
+      </c>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="25">
-        <f>+U5/T5-1</f>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="25">
+        <f>+Y5/X5-1</f>
         <v>4.6650124069478993E-2</v>
       </c>
-      <c r="V21" s="25">
-        <f>+V5/U5-1</f>
+      <c r="Z21" s="25">
+        <f>+Z5/Y5-1</f>
         <v>3.6510194404931307E-2</v>
       </c>
-      <c r="W21" s="25">
-        <f>+W5/V5-1</f>
+      <c r="AA21" s="25">
+        <f>+AA5/Z5-1</f>
         <v>3.7053979871912279E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
@@ -2179,7 +2316,7 @@
         <v>8.084680442638259E-2</v>
       </c>
       <c r="H22" s="26">
-        <f t="shared" ref="H22:N22" si="43">H8/D8-1</f>
+        <f t="shared" ref="H22:O22" si="43">H8/D8-1</f>
         <v>7.1453047221780475E-2</v>
       </c>
       <c r="I22" s="26">
@@ -2206,38 +2343,45 @@
         <f t="shared" si="43"/>
         <v>0.12232355746405044</v>
       </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="26">
-        <f t="shared" ref="Q22:T22" si="44">Q8/P8-1</f>
+      <c r="O22" s="26">
+        <f t="shared" si="43"/>
+        <v>0.205719351225915</v>
+      </c>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="26">
+        <f t="shared" ref="U22:X22" si="44">U8/T8-1</f>
         <v>6.0051297753646704E-2</v>
       </c>
-      <c r="R22" s="26">
+      <c r="V22" s="26">
         <f t="shared" si="44"/>
         <v>7.0446098155302561E-2</v>
       </c>
-      <c r="S22" s="26">
+      <c r="W22" s="26">
         <f t="shared" si="44"/>
         <v>0.17938511783068756</v>
       </c>
-      <c r="T22" s="26">
+      <c r="X22" s="26">
         <f t="shared" si="44"/>
         <v>-1.1652154624353428E-2</v>
       </c>
-      <c r="U22" s="26">
-        <f>U8/T8-1</f>
+      <c r="Y22" s="26">
+        <f>Y8/X8-1</f>
         <v>8.9919093718711096E-2</v>
       </c>
-      <c r="V22" s="26">
-        <f>V8/U8-1</f>
+      <c r="Z22" s="26">
+        <f>Z8/Y8-1</f>
         <v>3.691810267301654E-2</v>
       </c>
-      <c r="W22" s="26">
-        <f>W8/V8-1</f>
+      <c r="AA22" s="26">
+        <f>AA8/Z8-1</f>
         <v>7.6734497380144484E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
@@ -2289,299 +2433,327 @@
         <f t="shared" si="47"/>
         <v>0.27190350674931307</v>
       </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="25">
-        <f t="shared" ref="P23:T23" si="48">P10/P8</f>
+      <c r="O23" s="25">
+        <f t="shared" ref="O23" si="48">O10/O8</f>
+        <v>0.2961307889757816</v>
+      </c>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="25">
+        <f t="shared" ref="T23:X23" si="49">T10/T8</f>
         <v>0.28950630263099431</v>
       </c>
-      <c r="Q23" s="25">
-        <f t="shared" si="48"/>
+      <c r="U23" s="25">
+        <f t="shared" si="49"/>
         <v>0.28412936568198394</v>
       </c>
-      <c r="R23" s="25">
-        <f t="shared" si="48"/>
+      <c r="V23" s="25">
+        <f t="shared" si="49"/>
         <v>0.28074477870385656</v>
       </c>
-      <c r="S23" s="25">
-        <f t="shared" si="48"/>
+      <c r="W23" s="25">
+        <f t="shared" si="49"/>
         <v>0.27528387770849222</v>
       </c>
-      <c r="T23" s="25">
-        <f t="shared" si="48"/>
+      <c r="X23" s="25">
+        <f t="shared" si="49"/>
         <v>0.25404591580293134</v>
       </c>
-      <c r="U23" s="25">
-        <f>U10/U8</f>
+      <c r="Y23" s="25">
+        <f>Y10/Y8</f>
         <v>0.27361025386489557</v>
       </c>
-      <c r="V23" s="25">
-        <f>V10/V8</f>
+      <c r="Z23" s="25">
+        <f>Z10/Z8</f>
         <v>0.27775342761130933</v>
       </c>
-      <c r="W23" s="25">
-        <f>W10/W8</f>
+      <c r="AA23" s="25">
+        <f>AA10/AA8</f>
         <v>0.2770614559404892</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="25">
-        <f t="shared" ref="C24:J24" si="49">C12/C8</f>
+        <f t="shared" ref="C24:J24" si="50">C12/C8</f>
         <v>0.1014215453537799</v>
       </c>
       <c r="D24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.11299913574830713</v>
       </c>
       <c r="E24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.11170108971868987</v>
       </c>
       <c r="F24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.11299913574830713</v>
       </c>
       <c r="G24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.1216765845345484</v>
       </c>
       <c r="H24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.124677187921216</v>
       </c>
       <c r="I24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.11914293500315701</v>
       </c>
       <c r="J24" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.12364504449130408</v>
       </c>
       <c r="K24" s="25">
-        <f t="shared" ref="K24:L24" si="50">K12/K8</f>
+        <f t="shared" ref="K24:L24" si="51">K12/K8</f>
         <v>0.12165968468021171</v>
       </c>
       <c r="L24" s="25">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.11543795504265394</v>
       </c>
       <c r="M24" s="25">
-        <f t="shared" ref="M24:N24" si="51">M12/M8</f>
+        <f t="shared" ref="M24:N24" si="52">M12/M8</f>
         <v>0.11578365511826039</v>
       </c>
       <c r="N24" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.12269101452944689</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="25">
-        <f t="shared" ref="P24:T24" si="52">P12/P8</f>
+      <c r="O24" s="25">
+        <f t="shared" ref="O24" si="53">O12/O8</f>
+        <v>0.13377076956966466</v>
+      </c>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="25">
+        <f t="shared" ref="T24:X24" si="54">T12/T8</f>
         <v>0.14499008541513195</v>
       </c>
-      <c r="Q24" s="25">
-        <f t="shared" si="52"/>
+      <c r="U24" s="25">
+        <f t="shared" si="54"/>
         <v>0.13619704447700307</v>
       </c>
-      <c r="R24" s="25">
-        <f t="shared" si="52"/>
+      <c r="V24" s="25">
+        <f t="shared" si="54"/>
         <v>0.13380960358494534</v>
       </c>
-      <c r="S24" s="25">
-        <f t="shared" si="52"/>
+      <c r="W24" s="25">
+        <f t="shared" si="54"/>
         <v>0.12332617405442643</v>
       </c>
-      <c r="T24" s="25">
-        <f t="shared" si="52"/>
+      <c r="X24" s="25">
+        <f t="shared" si="54"/>
         <v>0.10645855821638087</v>
       </c>
-      <c r="U24" s="25">
-        <f>U12/U8</f>
+      <c r="Y24" s="25">
+        <f>Y12/Y8</f>
         <v>0.11324874523609792</v>
       </c>
-      <c r="V24" s="25">
-        <f>V12/V8</f>
+      <c r="Z24" s="25">
+        <f>Z12/Z8</f>
         <v>0.12237016427346423</v>
       </c>
-      <c r="W24" s="25">
-        <f>W12/W8</f>
+      <c r="AA24" s="25">
+        <f>AA12/AA8</f>
         <v>0.1190017792529845</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="25">
-        <f t="shared" ref="C25:J25" si="53">C16/C8</f>
+        <f t="shared" ref="C25:J25" si="55">C16/C8</f>
         <v>8.2806896855531067E-2</v>
       </c>
       <c r="D25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>9.0441254694872478E-2</v>
       </c>
       <c r="E25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>9.0830602115922754E-2</v>
       </c>
       <c r="F25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>9.0441254694872478E-2</v>
       </c>
       <c r="G25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.10044941743290078</v>
       </c>
       <c r="H25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>9.9698365150082693E-2</v>
       </c>
       <c r="I25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>9.6386093339175374E-2</v>
       </c>
       <c r="J25" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>9.924683865561873E-2</v>
       </c>
       <c r="K25" s="25">
-        <f t="shared" ref="K25:L25" si="54">K16/K8</f>
+        <f t="shared" ref="K25:L25" si="56">K16/K8</f>
         <v>9.6138773926668697E-2</v>
       </c>
       <c r="L25" s="25">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.1875752375771211E-2</v>
       </c>
       <c r="M25" s="25">
-        <f t="shared" ref="M25:N25" si="55">M16/M8</f>
+        <f t="shared" ref="M25:N25" si="57">M16/M8</f>
         <v>9.1401523956845879E-2</v>
       </c>
       <c r="N25" s="25">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>9.7334936832095223E-2</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="25">
-        <f t="shared" ref="P25:T25" si="56">P16/P8</f>
+      <c r="O25" s="25">
+        <f t="shared" ref="O25" si="58">O16/O8</f>
+        <v>0.1081385234713523</v>
+      </c>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="25">
+        <f t="shared" ref="T25:X25" si="59">T16/T8</f>
         <v>9.6482409429481844E-2</v>
       </c>
-      <c r="Q25" s="25">
-        <f t="shared" si="56"/>
+      <c r="U25" s="25">
+        <f t="shared" si="59"/>
         <v>0.10594671846928568</v>
       </c>
-      <c r="R25" s="25">
-        <f t="shared" si="56"/>
+      <c r="V25" s="25">
+        <f t="shared" si="59"/>
         <v>0.1035551119444372</v>
       </c>
-      <c r="S25" s="25">
-        <f t="shared" si="56"/>
+      <c r="W25" s="25">
+        <f t="shared" si="59"/>
         <v>9.1064008267180294E-2</v>
       </c>
-      <c r="T25" s="25">
-        <f t="shared" si="56"/>
+      <c r="X25" s="25">
+        <f t="shared" si="59"/>
         <v>8.0875846692864059E-2</v>
       </c>
-      <c r="U25" s="25">
-        <f>U16/U8</f>
+      <c r="Y25" s="25">
+        <f>Y16/Y8</f>
         <v>9.199221806648987E-2</v>
       </c>
-      <c r="V25" s="25">
-        <f>V16/V8</f>
+      <c r="Z25" s="25">
+        <f>Z16/Z8</f>
         <v>9.894970561855608E-2</v>
       </c>
-      <c r="W25" s="25">
-        <f>W16/W8</f>
+      <c r="AA25" s="25">
+        <f>AA16/AA8</f>
         <v>9.4285331626356952E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="25">
-        <f t="shared" ref="C26:J26" si="57">C15/C14</f>
+        <f t="shared" ref="C26:J26" si="60">C15/C14</f>
         <v>0.23614739715344146</v>
       </c>
       <c r="D26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.24969992636848723</v>
       </c>
       <c r="E26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.24620089985339466</v>
       </c>
       <c r="F26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.24969992636848723</v>
       </c>
       <c r="G26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.23400040498349459</v>
       </c>
       <c r="H26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.24969683685552918</v>
       </c>
       <c r="I26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.24420055570759933</v>
       </c>
       <c r="J26" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.23870200167108555</v>
       </c>
       <c r="K26" s="25">
-        <f t="shared" ref="K26:L26" si="58">K15/K14</f>
+        <f t="shared" ref="K26:L26" si="61">K15/K14</f>
         <v>0.25220049338486689</v>
       </c>
       <c r="L26" s="25">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.24249947809489722</v>
       </c>
       <c r="M26" s="25">
-        <f t="shared" ref="M26:N26" si="59">M15/M14</f>
+        <f t="shared" ref="M26:N26" si="62">M15/M14</f>
         <v>0.24979997010542232</v>
       </c>
       <c r="N26" s="25">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.23860019333694876</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="25">
-        <f t="shared" ref="P26:T26" si="60">P15/P14</f>
+      <c r="O26" s="25">
+        <f t="shared" ref="O26" si="63">O15/O14</f>
+        <v>0.22390041493775942</v>
+      </c>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="25">
+        <f t="shared" ref="T26:X26" si="64">T15/T14</f>
         <v>0.33205679525106302</v>
       </c>
-      <c r="Q26" s="25">
-        <f t="shared" si="60"/>
+      <c r="U26" s="25">
+        <f t="shared" si="64"/>
         <v>0.22596149157725784</v>
       </c>
-      <c r="R26" s="25">
-        <f t="shared" si="60"/>
+      <c r="V26" s="25">
+        <f t="shared" si="64"/>
         <v>0.2325753319336428</v>
       </c>
-      <c r="S26" s="25">
-        <f t="shared" si="60"/>
+      <c r="W26" s="25">
+        <f t="shared" si="64"/>
         <v>0.23729976002196115</v>
       </c>
-      <c r="T26" s="25">
-        <f t="shared" si="60"/>
+      <c r="X26" s="25">
+        <f t="shared" si="64"/>
         <v>0.23922044348421528</v>
       </c>
-      <c r="U26" s="25">
-        <f>U15/U14</f>
+      <c r="Y26" s="25">
+        <f>Y15/Y14</f>
         <v>0.24163184359779463</v>
       </c>
-      <c r="V26" s="25">
-        <f>V15/V14</f>
+      <c r="Z26" s="25">
+        <f>Z15/Z14</f>
         <v>0.24170720968070683</v>
       </c>
-      <c r="W26" s="25">
-        <f>W15/W14</f>
+      <c r="AA26" s="25">
+        <f>AA15/AA14</f>
         <v>0.24527603506773202</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2601,8 +2773,12 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+    </row>
+    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2622,8 +2798,12 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
-    </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2643,8 +2823,12 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
-    </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -2664,8 +2848,12 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
-    </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2685,8 +2873,12 @@
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
-    </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2706,8 +2898,12 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
-    </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -2727,8 +2923,12 @@
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
-    </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -2748,8 +2948,12 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -2769,8 +2973,12 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2790,8 +2998,12 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2811,8 +3023,12 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
-    </row>
-    <row r="38" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+    </row>
+    <row r="38" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2832,8 +3048,12 @@
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
-    </row>
-    <row r="39" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2853,8 +3073,12 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2874,8 +3098,12 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2895,8 +3123,12 @@
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
-    </row>
-    <row r="42" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+    </row>
+    <row r="42" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -2916,8 +3148,12 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
-    </row>
-    <row r="43" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2937,8 +3173,12 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
-    </row>
-    <row r="44" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2958,8 +3198,12 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
-    </row>
-    <row r="45" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+    </row>
+    <row r="45" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2979,8 +3223,12 @@
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
-    </row>
-    <row r="46" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3000,8 +3248,12 @@
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
-    </row>
-    <row r="47" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -3021,8 +3273,12 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
-    </row>
-    <row r="48" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
+    </row>
+    <row r="48" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -3042,8 +3298,12 @@
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -3063,8 +3323,12 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -3084,8 +3348,12 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -3105,8 +3373,12 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -3126,8 +3398,12 @@
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3147,8 +3423,12 @@
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3168,8 +3448,12 @@
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -3189,8 +3473,12 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -3210,8 +3498,12 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3231,8 +3523,12 @@
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -3252,8 +3548,12 @@
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -3273,8 +3573,12 @@
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -3294,8 +3598,12 @@
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -3315,8 +3623,12 @@
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3336,8 +3648,12 @@
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3357,8 +3673,12 @@
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3378,8 +3698,12 @@
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
-    </row>
-    <row r="65" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+    </row>
+    <row r="65" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3399,8 +3723,12 @@
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
-    </row>
-    <row r="66" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+    </row>
+    <row r="66" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3420,8 +3748,12 @@
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
-    </row>
-    <row r="67" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+    </row>
+    <row r="67" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3441,8 +3773,12 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3462,8 +3798,12 @@
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
-    </row>
-    <row r="69" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+    </row>
+    <row r="69" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3483,8 +3823,12 @@
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
-    </row>
-    <row r="70" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+    </row>
+    <row r="70" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -3504,8 +3848,12 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
-    </row>
-    <row r="71" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+    </row>
+    <row r="71" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -3525,8 +3873,12 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
-    </row>
-    <row r="72" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+    </row>
+    <row r="72" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -3546,8 +3898,12 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
-    </row>
-    <row r="73" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+    </row>
+    <row r="73" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -3567,8 +3923,12 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
-    </row>
-    <row r="74" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+    </row>
+    <row r="74" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -3588,8 +3948,12 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
-    </row>
-    <row r="75" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+    </row>
+    <row r="75" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3609,8 +3973,12 @@
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
-    </row>
-    <row r="76" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+    </row>
+    <row r="76" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3630,8 +3998,12 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
-    </row>
-    <row r="77" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+    </row>
+    <row r="77" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3651,8 +4023,12 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
-    </row>
-    <row r="78" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
+    </row>
+    <row r="78" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3672,8 +4048,12 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
-    </row>
-    <row r="79" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+    </row>
+    <row r="79" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3693,8 +4073,12 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
       <c r="U79" s="3"/>
-    </row>
-    <row r="80" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
+    </row>
+    <row r="80" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -3714,8 +4098,12 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -3735,8 +4123,12 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3756,8 +4148,12 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3777,8 +4173,12 @@
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
       <c r="U83" s="3"/>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -3798,8 +4198,12 @@
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -3819,8 +4223,12 @@
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
       <c r="U85" s="3"/>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -3840,8 +4248,12 @@
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -3861,8 +4273,12 @@
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -3882,8 +4298,12 @@
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -3903,8 +4323,12 @@
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
+      <c r="X89" s="3"/>
+      <c r="Y89" s="3"/>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -3924,8 +4348,12 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -3945,8 +4373,12 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
       <c r="U91" s="3"/>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+      <c r="X91" s="3"/>
+      <c r="Y91" s="3"/>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -3966,8 +4398,12 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
       <c r="U92" s="3"/>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -3987,8 +4423,12 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
       <c r="U93" s="3"/>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
+      <c r="X93" s="3"/>
+      <c r="Y93" s="3"/>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -4008,8 +4448,12 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
       <c r="U94" s="3"/>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -4029,8 +4473,12 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -4050,8 +4498,12 @@
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -4071,8 +4523,12 @@
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3"/>
+      <c r="W97" s="3"/>
+      <c r="X97" s="3"/>
+      <c r="Y97" s="3"/>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -4092,8 +4548,12 @@
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3"/>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -4113,8 +4573,12 @@
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3"/>
+      <c r="W99" s="3"/>
+      <c r="X99" s="3"/>
+      <c r="Y99" s="3"/>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -4134,8 +4598,12 @@
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3"/>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -4155,8 +4623,12 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3"/>
+      <c r="W101" s="3"/>
+      <c r="X101" s="3"/>
+      <c r="Y101" s="3"/>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -4176,8 +4648,12 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
-    </row>
-    <row r="103" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+      <c r="X102" s="3"/>
+      <c r="Y102" s="3"/>
+    </row>
+    <row r="103" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -4197,8 +4673,12 @@
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
-    </row>
-    <row r="104" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V103" s="3"/>
+      <c r="W103" s="3"/>
+      <c r="X103" s="3"/>
+      <c r="Y103" s="3"/>
+    </row>
+    <row r="104" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -4218,8 +4698,12 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
-    </row>
-    <row r="105" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V104" s="3"/>
+      <c r="W104" s="3"/>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
+    </row>
+    <row r="105" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -4239,8 +4723,12 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
-    </row>
-    <row r="106" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V105" s="3"/>
+      <c r="W105" s="3"/>
+      <c r="X105" s="3"/>
+      <c r="Y105" s="3"/>
+    </row>
+    <row r="106" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -4260,8 +4748,12 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
-    </row>
-    <row r="107" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V106" s="3"/>
+      <c r="W106" s="3"/>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
+    </row>
+    <row r="107" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -4281,8 +4773,12 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
-    </row>
-    <row r="108" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V107" s="3"/>
+      <c r="W107" s="3"/>
+      <c r="X107" s="3"/>
+      <c r="Y107" s="3"/>
+    </row>
+    <row r="108" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -4302,8 +4798,12 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
-    </row>
-    <row r="109" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V108" s="3"/>
+      <c r="W108" s="3"/>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3"/>
+    </row>
+    <row r="109" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -4323,8 +4823,12 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
-    </row>
-    <row r="110" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V109" s="3"/>
+      <c r="W109" s="3"/>
+      <c r="X109" s="3"/>
+      <c r="Y109" s="3"/>
+    </row>
+    <row r="110" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -4344,8 +4848,12 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
-    </row>
-    <row r="111" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V110" s="3"/>
+      <c r="W110" s="3"/>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3"/>
+    </row>
+    <row r="111" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -4365,8 +4873,12 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
       <c r="U111" s="3"/>
-    </row>
-    <row r="112" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V111" s="3"/>
+      <c r="W111" s="3"/>
+      <c r="X111" s="3"/>
+      <c r="Y111" s="3"/>
+    </row>
+    <row r="112" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -4386,8 +4898,12 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
-    </row>
-    <row r="113" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V112" s="3"/>
+      <c r="W112" s="3"/>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3"/>
+    </row>
+    <row r="113" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -4407,8 +4923,12 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
-    </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V113" s="3"/>
+      <c r="W113" s="3"/>
+      <c r="X113" s="3"/>
+      <c r="Y113" s="3"/>
+    </row>
+    <row r="114" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -4428,8 +4948,12 @@
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
-    </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V114" s="3"/>
+      <c r="W114" s="3"/>
+      <c r="X114" s="3"/>
+      <c r="Y114" s="3"/>
+    </row>
+    <row r="115" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -4449,8 +4973,12 @@
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
-    </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V115" s="3"/>
+      <c r="W115" s="3"/>
+      <c r="X115" s="3"/>
+      <c r="Y115" s="3"/>
+    </row>
+    <row r="116" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -4470,8 +4998,12 @@
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
       <c r="U116" s="3"/>
-    </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V116" s="3"/>
+      <c r="W116" s="3"/>
+      <c r="X116" s="3"/>
+      <c r="Y116" s="3"/>
+    </row>
+    <row r="117" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -4491,8 +5023,12 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
-    </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V117" s="3"/>
+      <c r="W117" s="3"/>
+      <c r="X117" s="3"/>
+      <c r="Y117" s="3"/>
+    </row>
+    <row r="118" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -4512,8 +5048,12 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
       <c r="U118" s="3"/>
-    </row>
-    <row r="119" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V118" s="3"/>
+      <c r="W118" s="3"/>
+      <c r="X118" s="3"/>
+      <c r="Y118" s="3"/>
+    </row>
+    <row r="119" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -4533,8 +5073,12 @@
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
       <c r="U119" s="3"/>
-    </row>
-    <row r="120" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V119" s="3"/>
+      <c r="W119" s="3"/>
+      <c r="X119" s="3"/>
+      <c r="Y119" s="3"/>
+    </row>
+    <row r="120" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -4554,8 +5098,12 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
-    </row>
-    <row r="121" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V120" s="3"/>
+      <c r="W120" s="3"/>
+      <c r="X120" s="3"/>
+      <c r="Y120" s="3"/>
+    </row>
+    <row r="121" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -4575,8 +5123,12 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
-    </row>
-    <row r="122" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V121" s="3"/>
+      <c r="W121" s="3"/>
+      <c r="X121" s="3"/>
+      <c r="Y121" s="3"/>
+    </row>
+    <row r="122" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -4596,8 +5148,12 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
       <c r="U122" s="3"/>
-    </row>
-    <row r="123" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V122" s="3"/>
+      <c r="W122" s="3"/>
+      <c r="X122" s="3"/>
+      <c r="Y122" s="3"/>
+    </row>
+    <row r="123" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -4617,8 +5173,12 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
       <c r="U123" s="3"/>
-    </row>
-    <row r="124" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V123" s="3"/>
+      <c r="W123" s="3"/>
+      <c r="X123" s="3"/>
+      <c r="Y123" s="3"/>
+    </row>
+    <row r="124" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -4638,8 +5198,12 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
-    </row>
-    <row r="125" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V124" s="3"/>
+      <c r="W124" s="3"/>
+      <c r="X124" s="3"/>
+      <c r="Y124" s="3"/>
+    </row>
+    <row r="125" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -4659,8 +5223,12 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
-    </row>
-    <row r="126" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V125" s="3"/>
+      <c r="W125" s="3"/>
+      <c r="X125" s="3"/>
+      <c r="Y125" s="3"/>
+    </row>
+    <row r="126" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -4680,8 +5248,12 @@
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
-    </row>
-    <row r="127" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V126" s="3"/>
+      <c r="W126" s="3"/>
+      <c r="X126" s="3"/>
+      <c r="Y126" s="3"/>
+    </row>
+    <row r="127" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -4701,8 +5273,12 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
       <c r="U127" s="3"/>
-    </row>
-    <row r="128" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V127" s="3"/>
+      <c r="W127" s="3"/>
+      <c r="X127" s="3"/>
+      <c r="Y127" s="3"/>
+    </row>
+    <row r="128" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -4722,8 +5298,12 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
-    </row>
-    <row r="129" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V128" s="3"/>
+      <c r="W128" s="3"/>
+      <c r="X128" s="3"/>
+      <c r="Y128" s="3"/>
+    </row>
+    <row r="129" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -4743,8 +5323,12 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
-    </row>
-    <row r="130" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V129" s="3"/>
+      <c r="W129" s="3"/>
+      <c r="X129" s="3"/>
+      <c r="Y129" s="3"/>
+    </row>
+    <row r="130" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -4764,8 +5348,12 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
       <c r="U130" s="3"/>
-    </row>
-    <row r="131" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V130" s="3"/>
+      <c r="W130" s="3"/>
+      <c r="X130" s="3"/>
+      <c r="Y130" s="3"/>
+    </row>
+    <row r="131" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -4785,8 +5373,12 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
       <c r="U131" s="3"/>
-    </row>
-    <row r="132" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V131" s="3"/>
+      <c r="W131" s="3"/>
+      <c r="X131" s="3"/>
+      <c r="Y131" s="3"/>
+    </row>
+    <row r="132" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -4806,8 +5398,12 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
       <c r="U132" s="3"/>
-    </row>
-    <row r="133" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V132" s="3"/>
+      <c r="W132" s="3"/>
+      <c r="X132" s="3"/>
+      <c r="Y132" s="3"/>
+    </row>
+    <row r="133" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -4827,8 +5423,12 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="3"/>
-    </row>
-    <row r="134" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V133" s="3"/>
+      <c r="W133" s="3"/>
+      <c r="X133" s="3"/>
+      <c r="Y133" s="3"/>
+    </row>
+    <row r="134" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -4848,8 +5448,12 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="3"/>
-    </row>
-    <row r="135" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V134" s="3"/>
+      <c r="W134" s="3"/>
+      <c r="X134" s="3"/>
+      <c r="Y134" s="3"/>
+    </row>
+    <row r="135" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -4869,8 +5473,12 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="3"/>
-    </row>
-    <row r="136" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V135" s="3"/>
+      <c r="W135" s="3"/>
+      <c r="X135" s="3"/>
+      <c r="Y135" s="3"/>
+    </row>
+    <row r="136" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -4890,8 +5498,12 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="3"/>
-    </row>
-    <row r="137" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V136" s="3"/>
+      <c r="W136" s="3"/>
+      <c r="X136" s="3"/>
+      <c r="Y136" s="3"/>
+    </row>
+    <row r="137" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -4911,8 +5523,12 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="3"/>
-    </row>
-    <row r="138" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V137" s="3"/>
+      <c r="W137" s="3"/>
+      <c r="X137" s="3"/>
+      <c r="Y137" s="3"/>
+    </row>
+    <row r="138" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -4932,8 +5548,12 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="3"/>
-    </row>
-    <row r="139" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V138" s="3"/>
+      <c r="W138" s="3"/>
+      <c r="X138" s="3"/>
+      <c r="Y138" s="3"/>
+    </row>
+    <row r="139" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -4953,8 +5573,12 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="3"/>
-    </row>
-    <row r="140" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V139" s="3"/>
+      <c r="W139" s="3"/>
+      <c r="X139" s="3"/>
+      <c r="Y139" s="3"/>
+    </row>
+    <row r="140" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -4974,8 +5598,12 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
-    </row>
-    <row r="141" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V140" s="3"/>
+      <c r="W140" s="3"/>
+      <c r="X140" s="3"/>
+      <c r="Y140" s="3"/>
+    </row>
+    <row r="141" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -4995,8 +5623,12 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
-    </row>
-    <row r="142" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V141" s="3"/>
+      <c r="W141" s="3"/>
+      <c r="X141" s="3"/>
+      <c r="Y141" s="3"/>
+    </row>
+    <row r="142" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -5016,8 +5648,12 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
-    </row>
-    <row r="143" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V142" s="3"/>
+      <c r="W142" s="3"/>
+      <c r="X142" s="3"/>
+      <c r="Y142" s="3"/>
+    </row>
+    <row r="143" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -5037,8 +5673,12 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="3"/>
-    </row>
-    <row r="144" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V143" s="3"/>
+      <c r="W143" s="3"/>
+      <c r="X143" s="3"/>
+      <c r="Y143" s="3"/>
+    </row>
+    <row r="144" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -5058,8 +5698,12 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="3"/>
-    </row>
-    <row r="145" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V144" s="3"/>
+      <c r="W144" s="3"/>
+      <c r="X144" s="3"/>
+      <c r="Y144" s="3"/>
+    </row>
+    <row r="145" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -5079,8 +5723,12 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
-    </row>
-    <row r="146" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V145" s="3"/>
+      <c r="W145" s="3"/>
+      <c r="X145" s="3"/>
+      <c r="Y145" s="3"/>
+    </row>
+    <row r="146" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -5100,8 +5748,12 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="3"/>
-    </row>
-    <row r="147" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V146" s="3"/>
+      <c r="W146" s="3"/>
+      <c r="X146" s="3"/>
+      <c r="Y146" s="3"/>
+    </row>
+    <row r="147" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -5121,8 +5773,12 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="3"/>
-    </row>
-    <row r="148" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V147" s="3"/>
+      <c r="W147" s="3"/>
+      <c r="X147" s="3"/>
+      <c r="Y147" s="3"/>
+    </row>
+    <row r="148" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -5142,8 +5798,12 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
-    </row>
-    <row r="149" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V148" s="3"/>
+      <c r="W148" s="3"/>
+      <c r="X148" s="3"/>
+      <c r="Y148" s="3"/>
+    </row>
+    <row r="149" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -5163,8 +5823,12 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
-    </row>
-    <row r="150" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V149" s="3"/>
+      <c r="W149" s="3"/>
+      <c r="X149" s="3"/>
+      <c r="Y149" s="3"/>
+    </row>
+    <row r="150" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -5184,8 +5848,12 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
-    </row>
-    <row r="151" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V150" s="3"/>
+      <c r="W150" s="3"/>
+      <c r="X150" s="3"/>
+      <c r="Y150" s="3"/>
+    </row>
+    <row r="151" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -5205,8 +5873,12 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
-    </row>
-    <row r="152" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V151" s="3"/>
+      <c r="W151" s="3"/>
+      <c r="X151" s="3"/>
+      <c r="Y151" s="3"/>
+    </row>
+    <row r="152" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -5226,8 +5898,12 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
-    </row>
-    <row r="153" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V152" s="3"/>
+      <c r="W152" s="3"/>
+      <c r="X152" s="3"/>
+      <c r="Y152" s="3"/>
+    </row>
+    <row r="153" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -5247,8 +5923,12 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="3"/>
-    </row>
-    <row r="154" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V153" s="3"/>
+      <c r="W153" s="3"/>
+      <c r="X153" s="3"/>
+      <c r="Y153" s="3"/>
+    </row>
+    <row r="154" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -5268,8 +5948,12 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
-    </row>
-    <row r="155" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V154" s="3"/>
+      <c r="W154" s="3"/>
+      <c r="X154" s="3"/>
+      <c r="Y154" s="3"/>
+    </row>
+    <row r="155" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -5289,8 +5973,12 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="3"/>
-    </row>
-    <row r="156" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V155" s="3"/>
+      <c r="W155" s="3"/>
+      <c r="X155" s="3"/>
+      <c r="Y155" s="3"/>
+    </row>
+    <row r="156" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -5310,8 +5998,12 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
-    </row>
-    <row r="157" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V156" s="3"/>
+      <c r="W156" s="3"/>
+      <c r="X156" s="3"/>
+      <c r="Y156" s="3"/>
+    </row>
+    <row r="157" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -5331,8 +6023,12 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
-    </row>
-    <row r="158" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V157" s="3"/>
+      <c r="W157" s="3"/>
+      <c r="X157" s="3"/>
+      <c r="Y157" s="3"/>
+    </row>
+    <row r="158" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -5352,8 +6048,12 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="3"/>
-    </row>
-    <row r="159" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V158" s="3"/>
+      <c r="W158" s="3"/>
+      <c r="X158" s="3"/>
+      <c r="Y158" s="3"/>
+    </row>
+    <row r="159" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -5373,8 +6073,12 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="3"/>
-    </row>
-    <row r="160" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V159" s="3"/>
+      <c r="W159" s="3"/>
+      <c r="X159" s="3"/>
+      <c r="Y159" s="3"/>
+    </row>
+    <row r="160" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -5394,8 +6098,12 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="3"/>
-    </row>
-    <row r="161" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V160" s="3"/>
+      <c r="W160" s="3"/>
+      <c r="X160" s="3"/>
+      <c r="Y160" s="3"/>
+    </row>
+    <row r="161" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -5415,8 +6123,12 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="3"/>
-    </row>
-    <row r="162" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V161" s="3"/>
+      <c r="W161" s="3"/>
+      <c r="X161" s="3"/>
+      <c r="Y161" s="3"/>
+    </row>
+    <row r="162" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -5436,8 +6148,12 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="3"/>
-    </row>
-    <row r="163" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V162" s="3"/>
+      <c r="W162" s="3"/>
+      <c r="X162" s="3"/>
+      <c r="Y162" s="3"/>
+    </row>
+    <row r="163" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -5457,8 +6173,12 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="3"/>
-    </row>
-    <row r="164" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V163" s="3"/>
+      <c r="W163" s="3"/>
+      <c r="X163" s="3"/>
+      <c r="Y163" s="3"/>
+    </row>
+    <row r="164" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -5478,8 +6198,12 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="3"/>
-    </row>
-    <row r="165" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V164" s="3"/>
+      <c r="W164" s="3"/>
+      <c r="X164" s="3"/>
+      <c r="Y164" s="3"/>
+    </row>
+    <row r="165" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -5499,8 +6223,12 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="3"/>
-    </row>
-    <row r="166" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V165" s="3"/>
+      <c r="W165" s="3"/>
+      <c r="X165" s="3"/>
+      <c r="Y165" s="3"/>
+    </row>
+    <row r="166" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -5520,8 +6248,12 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="3"/>
-    </row>
-    <row r="167" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V166" s="3"/>
+      <c r="W166" s="3"/>
+      <c r="X166" s="3"/>
+      <c r="Y166" s="3"/>
+    </row>
+    <row r="167" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -5541,8 +6273,12 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="3"/>
-    </row>
-    <row r="168" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V167" s="3"/>
+      <c r="W167" s="3"/>
+      <c r="X167" s="3"/>
+      <c r="Y167" s="3"/>
+    </row>
+    <row r="168" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -5562,8 +6298,12 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
-    </row>
-    <row r="169" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V168" s="3"/>
+      <c r="W168" s="3"/>
+      <c r="X168" s="3"/>
+      <c r="Y168" s="3"/>
+    </row>
+    <row r="169" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -5583,8 +6323,12 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="3"/>
-    </row>
-    <row r="170" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V169" s="3"/>
+      <c r="W169" s="3"/>
+      <c r="X169" s="3"/>
+      <c r="Y169" s="3"/>
+    </row>
+    <row r="170" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -5604,8 +6348,12 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="3"/>
-    </row>
-    <row r="171" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V170" s="3"/>
+      <c r="W170" s="3"/>
+      <c r="X170" s="3"/>
+      <c r="Y170" s="3"/>
+    </row>
+    <row r="171" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -5625,8 +6373,12 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="3"/>
-    </row>
-    <row r="172" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V171" s="3"/>
+      <c r="W171" s="3"/>
+      <c r="X171" s="3"/>
+      <c r="Y171" s="3"/>
+    </row>
+    <row r="172" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -5646,8 +6398,12 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
-    </row>
-    <row r="173" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V172" s="3"/>
+      <c r="W172" s="3"/>
+      <c r="X172" s="3"/>
+      <c r="Y172" s="3"/>
+    </row>
+    <row r="173" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -5667,8 +6423,12 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="3"/>
-    </row>
-    <row r="174" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V173" s="3"/>
+      <c r="W173" s="3"/>
+      <c r="X173" s="3"/>
+      <c r="Y173" s="3"/>
+    </row>
+    <row r="174" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -5688,8 +6448,12 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
-    </row>
-    <row r="175" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V174" s="3"/>
+      <c r="W174" s="3"/>
+      <c r="X174" s="3"/>
+      <c r="Y174" s="3"/>
+    </row>
+    <row r="175" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -5709,8 +6473,12 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="3"/>
-    </row>
-    <row r="176" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V175" s="3"/>
+      <c r="W175" s="3"/>
+      <c r="X175" s="3"/>
+      <c r="Y175" s="3"/>
+    </row>
+    <row r="176" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -5730,8 +6498,12 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
-    </row>
-    <row r="177" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V176" s="3"/>
+      <c r="W176" s="3"/>
+      <c r="X176" s="3"/>
+      <c r="Y176" s="3"/>
+    </row>
+    <row r="177" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -5751,8 +6523,12 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
-    </row>
-    <row r="178" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V177" s="3"/>
+      <c r="W177" s="3"/>
+      <c r="X177" s="3"/>
+      <c r="Y177" s="3"/>
+    </row>
+    <row r="178" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -5772,8 +6548,12 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="3"/>
-    </row>
-    <row r="179" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V178" s="3"/>
+      <c r="W178" s="3"/>
+      <c r="X178" s="3"/>
+      <c r="Y178" s="3"/>
+    </row>
+    <row r="179" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -5793,8 +6573,12 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="3"/>
-    </row>
-    <row r="180" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V179" s="3"/>
+      <c r="W179" s="3"/>
+      <c r="X179" s="3"/>
+      <c r="Y179" s="3"/>
+    </row>
+    <row r="180" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -5814,8 +6598,12 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
-    </row>
-    <row r="181" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V180" s="3"/>
+      <c r="W180" s="3"/>
+      <c r="X180" s="3"/>
+      <c r="Y180" s="3"/>
+    </row>
+    <row r="181" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -5835,8 +6623,12 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="3"/>
-    </row>
-    <row r="182" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V181" s="3"/>
+      <c r="W181" s="3"/>
+      <c r="X181" s="3"/>
+      <c r="Y181" s="3"/>
+    </row>
+    <row r="182" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -5856,8 +6648,12 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="3"/>
-    </row>
-    <row r="183" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V182" s="3"/>
+      <c r="W182" s="3"/>
+      <c r="X182" s="3"/>
+      <c r="Y182" s="3"/>
+    </row>
+    <row r="183" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -5877,8 +6673,12 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="3"/>
-    </row>
-    <row r="184" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V183" s="3"/>
+      <c r="W183" s="3"/>
+      <c r="X183" s="3"/>
+      <c r="Y183" s="3"/>
+    </row>
+    <row r="184" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -5898,8 +6698,12 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
-    </row>
-    <row r="185" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V184" s="3"/>
+      <c r="W184" s="3"/>
+      <c r="X184" s="3"/>
+      <c r="Y184" s="3"/>
+    </row>
+    <row r="185" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -5919,8 +6723,12 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="3"/>
-    </row>
-    <row r="186" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V185" s="3"/>
+      <c r="W185" s="3"/>
+      <c r="X185" s="3"/>
+      <c r="Y185" s="3"/>
+    </row>
+    <row r="186" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -5940,8 +6748,12 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
-    </row>
-    <row r="187" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V186" s="3"/>
+      <c r="W186" s="3"/>
+      <c r="X186" s="3"/>
+      <c r="Y186" s="3"/>
+    </row>
+    <row r="187" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -5961,8 +6773,12 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="3"/>
-    </row>
-    <row r="188" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V187" s="3"/>
+      <c r="W187" s="3"/>
+      <c r="X187" s="3"/>
+      <c r="Y187" s="3"/>
+    </row>
+    <row r="188" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -5982,8 +6798,12 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="3"/>
-    </row>
-    <row r="189" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V188" s="3"/>
+      <c r="W188" s="3"/>
+      <c r="X188" s="3"/>
+      <c r="Y188" s="3"/>
+    </row>
+    <row r="189" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -6003,8 +6823,12 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="3"/>
-    </row>
-    <row r="190" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V189" s="3"/>
+      <c r="W189" s="3"/>
+      <c r="X189" s="3"/>
+      <c r="Y189" s="3"/>
+    </row>
+    <row r="190" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -6024,8 +6848,12 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="3"/>
-    </row>
-    <row r="191" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V190" s="3"/>
+      <c r="W190" s="3"/>
+      <c r="X190" s="3"/>
+      <c r="Y190" s="3"/>
+    </row>
+    <row r="191" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -6045,8 +6873,12 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="3"/>
-    </row>
-    <row r="192" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V191" s="3"/>
+      <c r="W191" s="3"/>
+      <c r="X191" s="3"/>
+      <c r="Y191" s="3"/>
+    </row>
+    <row r="192" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -6066,8 +6898,12 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
-    </row>
-    <row r="193" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V192" s="3"/>
+      <c r="W192" s="3"/>
+      <c r="X192" s="3"/>
+      <c r="Y192" s="3"/>
+    </row>
+    <row r="193" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -6087,8 +6923,12 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="3"/>
-    </row>
-    <row r="194" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V193" s="3"/>
+      <c r="W193" s="3"/>
+      <c r="X193" s="3"/>
+      <c r="Y193" s="3"/>
+    </row>
+    <row r="194" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -6108,8 +6948,12 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="3"/>
-    </row>
-    <row r="195" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V194" s="3"/>
+      <c r="W194" s="3"/>
+      <c r="X194" s="3"/>
+      <c r="Y194" s="3"/>
+    </row>
+    <row r="195" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -6129,8 +6973,12 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="3"/>
-    </row>
-    <row r="196" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V195" s="3"/>
+      <c r="W195" s="3"/>
+      <c r="X195" s="3"/>
+      <c r="Y195" s="3"/>
+    </row>
+    <row r="196" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -6150,8 +6998,12 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
-    </row>
-    <row r="197" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V196" s="3"/>
+      <c r="W196" s="3"/>
+      <c r="X196" s="3"/>
+      <c r="Y196" s="3"/>
+    </row>
+    <row r="197" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -6171,8 +7023,12 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="3"/>
-    </row>
-    <row r="198" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V197" s="3"/>
+      <c r="W197" s="3"/>
+      <c r="X197" s="3"/>
+      <c r="Y197" s="3"/>
+    </row>
+    <row r="198" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -6192,8 +7048,12 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="3"/>
-    </row>
-    <row r="199" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V198" s="3"/>
+      <c r="W198" s="3"/>
+      <c r="X198" s="3"/>
+      <c r="Y198" s="3"/>
+    </row>
+    <row r="199" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -6213,8 +7073,12 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="3"/>
-    </row>
-    <row r="200" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V199" s="3"/>
+      <c r="W199" s="3"/>
+      <c r="X199" s="3"/>
+      <c r="Y199" s="3"/>
+    </row>
+    <row r="200" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -6234,8 +7098,12 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="3"/>
-    </row>
-    <row r="201" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V200" s="3"/>
+      <c r="W200" s="3"/>
+      <c r="X200" s="3"/>
+      <c r="Y200" s="3"/>
+    </row>
+    <row r="201" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -6255,8 +7123,12 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="3"/>
-    </row>
-    <row r="202" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V201" s="3"/>
+      <c r="W201" s="3"/>
+      <c r="X201" s="3"/>
+      <c r="Y201" s="3"/>
+    </row>
+    <row r="202" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -6276,8 +7148,12 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="3"/>
-    </row>
-    <row r="203" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V202" s="3"/>
+      <c r="W202" s="3"/>
+      <c r="X202" s="3"/>
+      <c r="Y202" s="3"/>
+    </row>
+    <row r="203" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -6297,8 +7173,12 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="3"/>
-    </row>
-    <row r="204" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V203" s="3"/>
+      <c r="W203" s="3"/>
+      <c r="X203" s="3"/>
+      <c r="Y203" s="3"/>
+    </row>
+    <row r="204" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -6318,8 +7198,12 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="3"/>
-    </row>
-    <row r="205" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V204" s="3"/>
+      <c r="W204" s="3"/>
+      <c r="X204" s="3"/>
+      <c r="Y204" s="3"/>
+    </row>
+    <row r="205" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -6339,8 +7223,12 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="3"/>
-    </row>
-    <row r="206" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V205" s="3"/>
+      <c r="W205" s="3"/>
+      <c r="X205" s="3"/>
+      <c r="Y205" s="3"/>
+    </row>
+    <row r="206" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -6360,8 +7248,12 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="3"/>
-    </row>
-    <row r="207" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V206" s="3"/>
+      <c r="W206" s="3"/>
+      <c r="X206" s="3"/>
+      <c r="Y206" s="3"/>
+    </row>
+    <row r="207" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -6381,8 +7273,12 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="3"/>
-    </row>
-    <row r="208" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V207" s="3"/>
+      <c r="W207" s="3"/>
+      <c r="X207" s="3"/>
+      <c r="Y207" s="3"/>
+    </row>
+    <row r="208" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -6402,8 +7298,12 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="3"/>
-    </row>
-    <row r="209" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V208" s="3"/>
+      <c r="W208" s="3"/>
+      <c r="X208" s="3"/>
+      <c r="Y208" s="3"/>
+    </row>
+    <row r="209" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -6423,8 +7323,12 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="3"/>
-    </row>
-    <row r="210" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V209" s="3"/>
+      <c r="W209" s="3"/>
+      <c r="X209" s="3"/>
+      <c r="Y209" s="3"/>
+    </row>
+    <row r="210" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -6444,8 +7348,12 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="3"/>
-    </row>
-    <row r="211" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V210" s="3"/>
+      <c r="W210" s="3"/>
+      <c r="X210" s="3"/>
+      <c r="Y210" s="3"/>
+    </row>
+    <row r="211" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -6465,8 +7373,12 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="3"/>
-    </row>
-    <row r="212" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V211" s="3"/>
+      <c r="W211" s="3"/>
+      <c r="X211" s="3"/>
+      <c r="Y211" s="3"/>
+    </row>
+    <row r="212" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -6486,8 +7398,12 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="3"/>
-    </row>
-    <row r="213" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V212" s="3"/>
+      <c r="W212" s="3"/>
+      <c r="X212" s="3"/>
+      <c r="Y212" s="3"/>
+    </row>
+    <row r="213" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -6507,8 +7423,12 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="3"/>
-    </row>
-    <row r="214" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V213" s="3"/>
+      <c r="W213" s="3"/>
+      <c r="X213" s="3"/>
+      <c r="Y213" s="3"/>
+    </row>
+    <row r="214" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -6528,8 +7448,12 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="3"/>
-    </row>
-    <row r="215" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V214" s="3"/>
+      <c r="W214" s="3"/>
+      <c r="X214" s="3"/>
+      <c r="Y214" s="3"/>
+    </row>
+    <row r="215" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -6549,8 +7473,12 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="3"/>
-    </row>
-    <row r="216" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V215" s="3"/>
+      <c r="W215" s="3"/>
+      <c r="X215" s="3"/>
+      <c r="Y215" s="3"/>
+    </row>
+    <row r="216" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -6570,8 +7498,12 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="3"/>
-    </row>
-    <row r="217" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V216" s="3"/>
+      <c r="W216" s="3"/>
+      <c r="X216" s="3"/>
+      <c r="Y216" s="3"/>
+    </row>
+    <row r="217" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -6591,8 +7523,12 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="3"/>
-    </row>
-    <row r="218" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V217" s="3"/>
+      <c r="W217" s="3"/>
+      <c r="X217" s="3"/>
+      <c r="Y217" s="3"/>
+    </row>
+    <row r="218" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -6612,8 +7548,12 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="3"/>
-    </row>
-    <row r="219" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V218" s="3"/>
+      <c r="W218" s="3"/>
+      <c r="X218" s="3"/>
+      <c r="Y218" s="3"/>
+    </row>
+    <row r="219" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -6633,8 +7573,12 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="3"/>
-    </row>
-    <row r="220" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V219" s="3"/>
+      <c r="W219" s="3"/>
+      <c r="X219" s="3"/>
+      <c r="Y219" s="3"/>
+    </row>
+    <row r="220" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -6654,8 +7598,12 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="3"/>
-    </row>
-    <row r="221" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V220" s="3"/>
+      <c r="W220" s="3"/>
+      <c r="X220" s="3"/>
+      <c r="Y220" s="3"/>
+    </row>
+    <row r="221" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -6675,8 +7623,12 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="3"/>
-    </row>
-    <row r="222" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V221" s="3"/>
+      <c r="W221" s="3"/>
+      <c r="X221" s="3"/>
+      <c r="Y221" s="3"/>
+    </row>
+    <row r="222" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -6696,8 +7648,12 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="3"/>
-    </row>
-    <row r="223" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V222" s="3"/>
+      <c r="W222" s="3"/>
+      <c r="X222" s="3"/>
+      <c r="Y222" s="3"/>
+    </row>
+    <row r="223" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -6717,8 +7673,12 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="3"/>
-    </row>
-    <row r="224" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V223" s="3"/>
+      <c r="W223" s="3"/>
+      <c r="X223" s="3"/>
+      <c r="Y223" s="3"/>
+    </row>
+    <row r="224" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -6738,8 +7698,12 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="3"/>
-    </row>
-    <row r="225" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V224" s="3"/>
+      <c r="W224" s="3"/>
+      <c r="X224" s="3"/>
+      <c r="Y224" s="3"/>
+    </row>
+    <row r="225" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -6759,8 +7723,12 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="3"/>
-    </row>
-    <row r="226" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V225" s="3"/>
+      <c r="W225" s="3"/>
+      <c r="X225" s="3"/>
+      <c r="Y225" s="3"/>
+    </row>
+    <row r="226" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -6780,8 +7748,12 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="3"/>
-    </row>
-    <row r="227" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V226" s="3"/>
+      <c r="W226" s="3"/>
+      <c r="X226" s="3"/>
+      <c r="Y226" s="3"/>
+    </row>
+    <row r="227" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -6801,8 +7773,12 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="3"/>
-    </row>
-    <row r="228" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V227" s="3"/>
+      <c r="W227" s="3"/>
+      <c r="X227" s="3"/>
+      <c r="Y227" s="3"/>
+    </row>
+    <row r="228" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -6822,8 +7798,12 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="3"/>
-    </row>
-    <row r="229" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V228" s="3"/>
+      <c r="W228" s="3"/>
+      <c r="X228" s="3"/>
+      <c r="Y228" s="3"/>
+    </row>
+    <row r="229" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -6843,8 +7823,12 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="3"/>
-    </row>
-    <row r="230" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V229" s="3"/>
+      <c r="W229" s="3"/>
+      <c r="X229" s="3"/>
+      <c r="Y229" s="3"/>
+    </row>
+    <row r="230" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -6864,8 +7848,12 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="3"/>
-    </row>
-    <row r="231" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V230" s="3"/>
+      <c r="W230" s="3"/>
+      <c r="X230" s="3"/>
+      <c r="Y230" s="3"/>
+    </row>
+    <row r="231" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -6885,8 +7873,12 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="3"/>
-    </row>
-    <row r="232" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V231" s="3"/>
+      <c r="W231" s="3"/>
+      <c r="X231" s="3"/>
+      <c r="Y231" s="3"/>
+    </row>
+    <row r="232" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -6906,8 +7898,12 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="3"/>
-    </row>
-    <row r="233" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V232" s="3"/>
+      <c r="W232" s="3"/>
+      <c r="X232" s="3"/>
+      <c r="Y232" s="3"/>
+    </row>
+    <row r="233" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -6927,8 +7923,12 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="3"/>
-    </row>
-    <row r="234" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V233" s="3"/>
+      <c r="W233" s="3"/>
+      <c r="X233" s="3"/>
+      <c r="Y233" s="3"/>
+    </row>
+    <row r="234" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -6948,8 +7948,12 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="3"/>
-    </row>
-    <row r="235" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V234" s="3"/>
+      <c r="W234" s="3"/>
+      <c r="X234" s="3"/>
+      <c r="Y234" s="3"/>
+    </row>
+    <row r="235" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -6969,8 +7973,12 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="3"/>
-    </row>
-    <row r="236" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V235" s="3"/>
+      <c r="W235" s="3"/>
+      <c r="X235" s="3"/>
+      <c r="Y235" s="3"/>
+    </row>
+    <row r="236" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -6990,8 +7998,12 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="3"/>
-    </row>
-    <row r="237" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V236" s="3"/>
+      <c r="W236" s="3"/>
+      <c r="X236" s="3"/>
+      <c r="Y236" s="3"/>
+    </row>
+    <row r="237" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -7011,8 +8023,12 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="3"/>
-    </row>
-    <row r="238" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V237" s="3"/>
+      <c r="W237" s="3"/>
+      <c r="X237" s="3"/>
+      <c r="Y237" s="3"/>
+    </row>
+    <row r="238" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -7032,8 +8048,12 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="3"/>
-    </row>
-    <row r="239" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V238" s="3"/>
+      <c r="W238" s="3"/>
+      <c r="X238" s="3"/>
+      <c r="Y238" s="3"/>
+    </row>
+    <row r="239" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -7053,8 +8073,12 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="3"/>
-    </row>
-    <row r="240" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V239" s="3"/>
+      <c r="W239" s="3"/>
+      <c r="X239" s="3"/>
+      <c r="Y239" s="3"/>
+    </row>
+    <row r="240" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -7074,8 +8098,12 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="3"/>
-    </row>
-    <row r="241" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V240" s="3"/>
+      <c r="W240" s="3"/>
+      <c r="X240" s="3"/>
+      <c r="Y240" s="3"/>
+    </row>
+    <row r="241" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -7095,8 +8123,12 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="3"/>
-    </row>
-    <row r="242" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V241" s="3"/>
+      <c r="W241" s="3"/>
+      <c r="X241" s="3"/>
+      <c r="Y241" s="3"/>
+    </row>
+    <row r="242" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -7116,8 +8148,12 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="3"/>
-    </row>
-    <row r="243" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V242" s="3"/>
+      <c r="W242" s="3"/>
+      <c r="X242" s="3"/>
+      <c r="Y242" s="3"/>
+    </row>
+    <row r="243" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -7137,8 +8173,12 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="3"/>
-    </row>
-    <row r="244" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V243" s="3"/>
+      <c r="W243" s="3"/>
+      <c r="X243" s="3"/>
+      <c r="Y243" s="3"/>
+    </row>
+    <row r="244" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -7158,8 +8198,12 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="3"/>
-    </row>
-    <row r="245" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V244" s="3"/>
+      <c r="W244" s="3"/>
+      <c r="X244" s="3"/>
+      <c r="Y244" s="3"/>
+    </row>
+    <row r="245" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -7179,8 +8223,12 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="3"/>
-    </row>
-    <row r="246" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V245" s="3"/>
+      <c r="W245" s="3"/>
+      <c r="X245" s="3"/>
+      <c r="Y245" s="3"/>
+    </row>
+    <row r="246" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -7200,8 +8248,12 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="3"/>
-    </row>
-    <row r="247" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V246" s="3"/>
+      <c r="W246" s="3"/>
+      <c r="X246" s="3"/>
+      <c r="Y246" s="3"/>
+    </row>
+    <row r="247" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -7221,8 +8273,12 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="3"/>
-    </row>
-    <row r="248" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V247" s="3"/>
+      <c r="W247" s="3"/>
+      <c r="X247" s="3"/>
+      <c r="Y247" s="3"/>
+    </row>
+    <row r="248" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -7242,8 +8298,12 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="3"/>
-    </row>
-    <row r="249" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V248" s="3"/>
+      <c r="W248" s="3"/>
+      <c r="X248" s="3"/>
+      <c r="Y248" s="3"/>
+    </row>
+    <row r="249" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -7263,8 +8323,12 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="3"/>
-    </row>
-    <row r="250" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V249" s="3"/>
+      <c r="W249" s="3"/>
+      <c r="X249" s="3"/>
+      <c r="Y249" s="3"/>
+    </row>
+    <row r="250" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -7284,8 +8348,12 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="3"/>
-    </row>
-    <row r="251" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V250" s="3"/>
+      <c r="W250" s="3"/>
+      <c r="X250" s="3"/>
+      <c r="Y250" s="3"/>
+    </row>
+    <row r="251" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -7305,8 +8373,12 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="3"/>
-    </row>
-    <row r="252" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V251" s="3"/>
+      <c r="W251" s="3"/>
+      <c r="X251" s="3"/>
+      <c r="Y251" s="3"/>
+    </row>
+    <row r="252" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -7326,8 +8398,12 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="3"/>
-    </row>
-    <row r="253" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V252" s="3"/>
+      <c r="W252" s="3"/>
+      <c r="X252" s="3"/>
+      <c r="Y252" s="3"/>
+    </row>
+    <row r="253" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -7347,8 +8423,12 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="3"/>
-    </row>
-    <row r="254" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V253" s="3"/>
+      <c r="W253" s="3"/>
+      <c r="X253" s="3"/>
+      <c r="Y253" s="3"/>
+    </row>
+    <row r="254" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -7368,8 +8448,12 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="3"/>
-    </row>
-    <row r="255" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V254" s="3"/>
+      <c r="W254" s="3"/>
+      <c r="X254" s="3"/>
+      <c r="Y254" s="3"/>
+    </row>
+    <row r="255" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -7389,8 +8473,12 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="3"/>
-    </row>
-    <row r="256" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V255" s="3"/>
+      <c r="W255" s="3"/>
+      <c r="X255" s="3"/>
+      <c r="Y255" s="3"/>
+    </row>
+    <row r="256" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -7410,8 +8498,12 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="3"/>
-    </row>
-    <row r="257" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V256" s="3"/>
+      <c r="W256" s="3"/>
+      <c r="X256" s="3"/>
+      <c r="Y256" s="3"/>
+    </row>
+    <row r="257" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -7431,8 +8523,12 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="3"/>
-    </row>
-    <row r="258" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V257" s="3"/>
+      <c r="W257" s="3"/>
+      <c r="X257" s="3"/>
+      <c r="Y257" s="3"/>
+    </row>
+    <row r="258" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -7452,8 +8548,12 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="3"/>
-    </row>
-    <row r="259" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V258" s="3"/>
+      <c r="W258" s="3"/>
+      <c r="X258" s="3"/>
+      <c r="Y258" s="3"/>
+    </row>
+    <row r="259" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -7473,8 +8573,12 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="3"/>
-    </row>
-    <row r="260" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V259" s="3"/>
+      <c r="W259" s="3"/>
+      <c r="X259" s="3"/>
+      <c r="Y259" s="3"/>
+    </row>
+    <row r="260" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -7494,8 +8598,12 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="3"/>
-    </row>
-    <row r="261" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V260" s="3"/>
+      <c r="W260" s="3"/>
+      <c r="X260" s="3"/>
+      <c r="Y260" s="3"/>
+    </row>
+    <row r="261" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -7515,8 +8623,12 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="3"/>
-    </row>
-    <row r="262" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V261" s="3"/>
+      <c r="W261" s="3"/>
+      <c r="X261" s="3"/>
+      <c r="Y261" s="3"/>
+    </row>
+    <row r="262" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -7536,8 +8648,12 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="3"/>
-    </row>
-    <row r="263" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V262" s="3"/>
+      <c r="W262" s="3"/>
+      <c r="X262" s="3"/>
+      <c r="Y262" s="3"/>
+    </row>
+    <row r="263" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -7557,8 +8673,12 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="3"/>
-    </row>
-    <row r="264" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V263" s="3"/>
+      <c r="W263" s="3"/>
+      <c r="X263" s="3"/>
+      <c r="Y263" s="3"/>
+    </row>
+    <row r="264" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -7578,8 +8698,12 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="3"/>
-    </row>
-    <row r="265" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V264" s="3"/>
+      <c r="W264" s="3"/>
+      <c r="X264" s="3"/>
+      <c r="Y264" s="3"/>
+    </row>
+    <row r="265" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -7599,8 +8723,12 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="3"/>
-    </row>
-    <row r="266" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V265" s="3"/>
+      <c r="W265" s="3"/>
+      <c r="X265" s="3"/>
+      <c r="Y265" s="3"/>
+    </row>
+    <row r="266" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -7620,8 +8748,12 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="3"/>
-    </row>
-    <row r="267" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V266" s="3"/>
+      <c r="W266" s="3"/>
+      <c r="X266" s="3"/>
+      <c r="Y266" s="3"/>
+    </row>
+    <row r="267" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -7641,8 +8773,12 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="3"/>
-    </row>
-    <row r="268" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V267" s="3"/>
+      <c r="W267" s="3"/>
+      <c r="X267" s="3"/>
+      <c r="Y267" s="3"/>
+    </row>
+    <row r="268" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -7662,8 +8798,12 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="3"/>
-    </row>
-    <row r="269" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V268" s="3"/>
+      <c r="W268" s="3"/>
+      <c r="X268" s="3"/>
+      <c r="Y268" s="3"/>
+    </row>
+    <row r="269" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -7683,8 +8823,12 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="3"/>
-    </row>
-    <row r="270" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V269" s="3"/>
+      <c r="W269" s="3"/>
+      <c r="X269" s="3"/>
+      <c r="Y269" s="3"/>
+    </row>
+    <row r="270" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -7704,8 +8848,12 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="3"/>
-    </row>
-    <row r="271" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V270" s="3"/>
+      <c r="W270" s="3"/>
+      <c r="X270" s="3"/>
+      <c r="Y270" s="3"/>
+    </row>
+    <row r="271" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -7725,8 +8873,12 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="3"/>
-    </row>
-    <row r="272" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V271" s="3"/>
+      <c r="W271" s="3"/>
+      <c r="X271" s="3"/>
+      <c r="Y271" s="3"/>
+    </row>
+    <row r="272" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -7746,8 +8898,12 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="3"/>
-    </row>
-    <row r="273" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V272" s="3"/>
+      <c r="W272" s="3"/>
+      <c r="X272" s="3"/>
+      <c r="Y272" s="3"/>
+    </row>
+    <row r="273" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -7767,8 +8923,12 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="3"/>
-    </row>
-    <row r="274" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V273" s="3"/>
+      <c r="W273" s="3"/>
+      <c r="X273" s="3"/>
+      <c r="Y273" s="3"/>
+    </row>
+    <row r="274" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -7788,8 +8948,12 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="3"/>
-    </row>
-    <row r="275" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V274" s="3"/>
+      <c r="W274" s="3"/>
+      <c r="X274" s="3"/>
+      <c r="Y274" s="3"/>
+    </row>
+    <row r="275" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -7809,8 +8973,12 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="3"/>
-    </row>
-    <row r="276" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V275" s="3"/>
+      <c r="W275" s="3"/>
+      <c r="X275" s="3"/>
+      <c r="Y275" s="3"/>
+    </row>
+    <row r="276" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -7830,8 +8998,12 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="3"/>
-    </row>
-    <row r="277" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V276" s="3"/>
+      <c r="W276" s="3"/>
+      <c r="X276" s="3"/>
+      <c r="Y276" s="3"/>
+    </row>
+    <row r="277" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -7851,8 +9023,12 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="3"/>
-    </row>
-    <row r="278" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V277" s="3"/>
+      <c r="W277" s="3"/>
+      <c r="X277" s="3"/>
+      <c r="Y277" s="3"/>
+    </row>
+    <row r="278" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -7872,8 +9048,12 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="3"/>
-    </row>
-    <row r="279" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V278" s="3"/>
+      <c r="W278" s="3"/>
+      <c r="X278" s="3"/>
+      <c r="Y278" s="3"/>
+    </row>
+    <row r="279" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -7893,8 +9073,12 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="3"/>
-    </row>
-    <row r="280" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V279" s="3"/>
+      <c r="W279" s="3"/>
+      <c r="X279" s="3"/>
+      <c r="Y279" s="3"/>
+    </row>
+    <row r="280" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -7914,8 +9098,12 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="3"/>
-    </row>
-    <row r="281" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V280" s="3"/>
+      <c r="W280" s="3"/>
+      <c r="X280" s="3"/>
+      <c r="Y280" s="3"/>
+    </row>
+    <row r="281" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -7935,8 +9123,12 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="3"/>
-    </row>
-    <row r="282" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V281" s="3"/>
+      <c r="W281" s="3"/>
+      <c r="X281" s="3"/>
+      <c r="Y281" s="3"/>
+    </row>
+    <row r="282" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -7956,8 +9148,12 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="3"/>
-    </row>
-    <row r="283" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V282" s="3"/>
+      <c r="W282" s="3"/>
+      <c r="X282" s="3"/>
+      <c r="Y282" s="3"/>
+    </row>
+    <row r="283" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -7977,8 +9173,12 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="3"/>
-    </row>
-    <row r="284" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V283" s="3"/>
+      <c r="W283" s="3"/>
+      <c r="X283" s="3"/>
+      <c r="Y283" s="3"/>
+    </row>
+    <row r="284" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -7998,8 +9198,12 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="3"/>
-    </row>
-    <row r="285" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V284" s="3"/>
+      <c r="W284" s="3"/>
+      <c r="X284" s="3"/>
+      <c r="Y284" s="3"/>
+    </row>
+    <row r="285" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -8019,8 +9223,12 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="3"/>
-    </row>
-    <row r="286" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V285" s="3"/>
+      <c r="W285" s="3"/>
+      <c r="X285" s="3"/>
+      <c r="Y285" s="3"/>
+    </row>
+    <row r="286" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -8040,8 +9248,12 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="3"/>
-    </row>
-    <row r="287" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V286" s="3"/>
+      <c r="W286" s="3"/>
+      <c r="X286" s="3"/>
+      <c r="Y286" s="3"/>
+    </row>
+    <row r="287" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -8061,8 +9273,12 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="3"/>
-    </row>
-    <row r="288" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V287" s="3"/>
+      <c r="W287" s="3"/>
+      <c r="X287" s="3"/>
+      <c r="Y287" s="3"/>
+    </row>
+    <row r="288" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -8082,8 +9298,12 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="3"/>
-    </row>
-    <row r="289" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V288" s="3"/>
+      <c r="W288" s="3"/>
+      <c r="X288" s="3"/>
+      <c r="Y288" s="3"/>
+    </row>
+    <row r="289" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -8103,8 +9323,12 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="3"/>
-    </row>
-    <row r="290" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V289" s="3"/>
+      <c r="W289" s="3"/>
+      <c r="X289" s="3"/>
+      <c r="Y289" s="3"/>
+    </row>
+    <row r="290" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -8124,8 +9348,12 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="3"/>
-    </row>
-    <row r="291" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V290" s="3"/>
+      <c r="W290" s="3"/>
+      <c r="X290" s="3"/>
+      <c r="Y290" s="3"/>
+    </row>
+    <row r="291" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -8145,8 +9373,12 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="3"/>
-    </row>
-    <row r="292" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V291" s="3"/>
+      <c r="W291" s="3"/>
+      <c r="X291" s="3"/>
+      <c r="Y291" s="3"/>
+    </row>
+    <row r="292" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -8166,8 +9398,12 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="3"/>
-    </row>
-    <row r="293" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V292" s="3"/>
+      <c r="W292" s="3"/>
+      <c r="X292" s="3"/>
+      <c r="Y292" s="3"/>
+    </row>
+    <row r="293" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -8187,8 +9423,12 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="3"/>
-    </row>
-    <row r="294" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V293" s="3"/>
+      <c r="W293" s="3"/>
+      <c r="X293" s="3"/>
+      <c r="Y293" s="3"/>
+    </row>
+    <row r="294" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -8208,8 +9448,12 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="3"/>
-    </row>
-    <row r="295" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V294" s="3"/>
+      <c r="W294" s="3"/>
+      <c r="X294" s="3"/>
+      <c r="Y294" s="3"/>
+    </row>
+    <row r="295" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -8229,8 +9473,12 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="3"/>
-    </row>
-    <row r="296" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V295" s="3"/>
+      <c r="W295" s="3"/>
+      <c r="X295" s="3"/>
+      <c r="Y295" s="3"/>
+    </row>
+    <row r="296" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -8250,8 +9498,12 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="3"/>
-    </row>
-    <row r="297" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V296" s="3"/>
+      <c r="W296" s="3"/>
+      <c r="X296" s="3"/>
+      <c r="Y296" s="3"/>
+    </row>
+    <row r="297" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -8271,8 +9523,12 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="3"/>
-    </row>
-    <row r="298" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V297" s="3"/>
+      <c r="W297" s="3"/>
+      <c r="X297" s="3"/>
+      <c r="Y297" s="3"/>
+    </row>
+    <row r="298" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -8292,8 +9548,12 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="3"/>
-    </row>
-    <row r="299" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V298" s="3"/>
+      <c r="W298" s="3"/>
+      <c r="X298" s="3"/>
+      <c r="Y298" s="3"/>
+    </row>
+    <row r="299" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -8313,8 +9573,12 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="3"/>
-    </row>
-    <row r="300" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V299" s="3"/>
+      <c r="W299" s="3"/>
+      <c r="X299" s="3"/>
+      <c r="Y299" s="3"/>
+    </row>
+    <row r="300" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -8334,8 +9598,12 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="3"/>
-    </row>
-    <row r="301" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V300" s="3"/>
+      <c r="W300" s="3"/>
+      <c r="X300" s="3"/>
+      <c r="Y300" s="3"/>
+    </row>
+    <row r="301" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -8355,8 +9623,12 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="3"/>
-    </row>
-    <row r="302" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V301" s="3"/>
+      <c r="W301" s="3"/>
+      <c r="X301" s="3"/>
+      <c r="Y301" s="3"/>
+    </row>
+    <row r="302" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -8376,8 +9648,12 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="3"/>
-    </row>
-    <row r="303" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V302" s="3"/>
+      <c r="W302" s="3"/>
+      <c r="X302" s="3"/>
+      <c r="Y302" s="3"/>
+    </row>
+    <row r="303" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -8397,8 +9673,12 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="3"/>
-    </row>
-    <row r="304" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V303" s="3"/>
+      <c r="W303" s="3"/>
+      <c r="X303" s="3"/>
+      <c r="Y303" s="3"/>
+    </row>
+    <row r="304" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -8418,8 +9698,12 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="3"/>
-    </row>
-    <row r="305" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V304" s="3"/>
+      <c r="W304" s="3"/>
+      <c r="X304" s="3"/>
+      <c r="Y304" s="3"/>
+    </row>
+    <row r="305" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -8439,8 +9723,12 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="3"/>
-    </row>
-    <row r="306" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V305" s="3"/>
+      <c r="W305" s="3"/>
+      <c r="X305" s="3"/>
+      <c r="Y305" s="3"/>
+    </row>
+    <row r="306" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -8460,8 +9748,12 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="3"/>
-    </row>
-    <row r="307" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V306" s="3"/>
+      <c r="W306" s="3"/>
+      <c r="X306" s="3"/>
+      <c r="Y306" s="3"/>
+    </row>
+    <row r="307" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -8481,8 +9773,12 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="3"/>
-    </row>
-    <row r="308" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V307" s="3"/>
+      <c r="W307" s="3"/>
+      <c r="X307" s="3"/>
+      <c r="Y307" s="3"/>
+    </row>
+    <row r="308" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -8502,8 +9798,12 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="3"/>
-    </row>
-    <row r="309" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V308" s="3"/>
+      <c r="W308" s="3"/>
+      <c r="X308" s="3"/>
+      <c r="Y308" s="3"/>
+    </row>
+    <row r="309" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -8523,8 +9823,12 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="3"/>
-    </row>
-    <row r="310" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V309" s="3"/>
+      <c r="W309" s="3"/>
+      <c r="X309" s="3"/>
+      <c r="Y309" s="3"/>
+    </row>
+    <row r="310" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -8544,8 +9848,12 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="3"/>
-    </row>
-    <row r="311" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V310" s="3"/>
+      <c r="W310" s="3"/>
+      <c r="X310" s="3"/>
+      <c r="Y310" s="3"/>
+    </row>
+    <row r="311" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -8565,8 +9873,12 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="3"/>
-    </row>
-    <row r="312" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V311" s="3"/>
+      <c r="W311" s="3"/>
+      <c r="X311" s="3"/>
+      <c r="Y311" s="3"/>
+    </row>
+    <row r="312" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -8586,8 +9898,12 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="3"/>
-    </row>
-    <row r="313" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V312" s="3"/>
+      <c r="W312" s="3"/>
+      <c r="X312" s="3"/>
+      <c r="Y312" s="3"/>
+    </row>
+    <row r="313" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -8607,8 +9923,12 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="3"/>
-    </row>
-    <row r="314" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V313" s="3"/>
+      <c r="W313" s="3"/>
+      <c r="X313" s="3"/>
+      <c r="Y313" s="3"/>
+    </row>
+    <row r="314" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -8628,8 +9948,12 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="3"/>
-    </row>
-    <row r="315" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V314" s="3"/>
+      <c r="W314" s="3"/>
+      <c r="X314" s="3"/>
+      <c r="Y314" s="3"/>
+    </row>
+    <row r="315" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -8649,8 +9973,12 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="3"/>
-    </row>
-    <row r="316" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V315" s="3"/>
+      <c r="W315" s="3"/>
+      <c r="X315" s="3"/>
+      <c r="Y315" s="3"/>
+    </row>
+    <row r="316" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -8670,8 +9998,12 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="3"/>
-    </row>
-    <row r="317" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V316" s="3"/>
+      <c r="W316" s="3"/>
+      <c r="X316" s="3"/>
+      <c r="Y316" s="3"/>
+    </row>
+    <row r="317" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -8691,8 +10023,12 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="3"/>
-    </row>
-    <row r="318" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V317" s="3"/>
+      <c r="W317" s="3"/>
+      <c r="X317" s="3"/>
+      <c r="Y317" s="3"/>
+    </row>
+    <row r="318" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -8712,8 +10048,12 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="3"/>
-    </row>
-    <row r="319" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V318" s="3"/>
+      <c r="W318" s="3"/>
+      <c r="X318" s="3"/>
+      <c r="Y318" s="3"/>
+    </row>
+    <row r="319" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -8733,8 +10073,12 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="3"/>
-    </row>
-    <row r="320" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V319" s="3"/>
+      <c r="W319" s="3"/>
+      <c r="X319" s="3"/>
+      <c r="Y319" s="3"/>
+    </row>
+    <row r="320" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -8754,8 +10098,12 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="3"/>
-    </row>
-    <row r="321" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V320" s="3"/>
+      <c r="W320" s="3"/>
+      <c r="X320" s="3"/>
+      <c r="Y320" s="3"/>
+    </row>
+    <row r="321" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -8775,8 +10123,12 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="3"/>
-    </row>
-    <row r="322" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V321" s="3"/>
+      <c r="W321" s="3"/>
+      <c r="X321" s="3"/>
+      <c r="Y321" s="3"/>
+    </row>
+    <row r="322" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -8796,8 +10148,12 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="3"/>
-    </row>
-    <row r="323" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V322" s="3"/>
+      <c r="W322" s="3"/>
+      <c r="X322" s="3"/>
+      <c r="Y322" s="3"/>
+    </row>
+    <row r="323" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -8817,8 +10173,12 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="3"/>
-    </row>
-    <row r="324" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V323" s="3"/>
+      <c r="W323" s="3"/>
+      <c r="X323" s="3"/>
+      <c r="Y323" s="3"/>
+    </row>
+    <row r="324" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -8838,8 +10198,12 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="3"/>
-    </row>
-    <row r="325" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V324" s="3"/>
+      <c r="W324" s="3"/>
+      <c r="X324" s="3"/>
+      <c r="Y324" s="3"/>
+    </row>
+    <row r="325" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -8859,8 +10223,12 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="3"/>
-    </row>
-    <row r="326" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V325" s="3"/>
+      <c r="W325" s="3"/>
+      <c r="X325" s="3"/>
+      <c r="Y325" s="3"/>
+    </row>
+    <row r="326" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -8880,8 +10248,12 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="3"/>
-    </row>
-    <row r="327" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V326" s="3"/>
+      <c r="W326" s="3"/>
+      <c r="X326" s="3"/>
+      <c r="Y326" s="3"/>
+    </row>
+    <row r="327" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -8901,8 +10273,12 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="3"/>
-    </row>
-    <row r="328" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V327" s="3"/>
+      <c r="W327" s="3"/>
+      <c r="X327" s="3"/>
+      <c r="Y327" s="3"/>
+    </row>
+    <row r="328" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -8922,8 +10298,12 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="3"/>
-    </row>
-    <row r="329" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V328" s="3"/>
+      <c r="W328" s="3"/>
+      <c r="X328" s="3"/>
+      <c r="Y328" s="3"/>
+    </row>
+    <row r="329" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -8943,8 +10323,12 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="3"/>
-    </row>
-    <row r="330" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V329" s="3"/>
+      <c r="W329" s="3"/>
+      <c r="X329" s="3"/>
+      <c r="Y329" s="3"/>
+    </row>
+    <row r="330" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -8964,8 +10348,12 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="3"/>
-    </row>
-    <row r="331" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V330" s="3"/>
+      <c r="W330" s="3"/>
+      <c r="X330" s="3"/>
+      <c r="Y330" s="3"/>
+    </row>
+    <row r="331" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -8985,8 +10373,12 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="3"/>
-    </row>
-    <row r="332" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V331" s="3"/>
+      <c r="W331" s="3"/>
+      <c r="X331" s="3"/>
+      <c r="Y331" s="3"/>
+    </row>
+    <row r="332" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -9006,8 +10398,12 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="3"/>
-    </row>
-    <row r="333" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V332" s="3"/>
+      <c r="W332" s="3"/>
+      <c r="X332" s="3"/>
+      <c r="Y332" s="3"/>
+    </row>
+    <row r="333" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -9027,8 +10423,12 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="3"/>
-    </row>
-    <row r="334" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V333" s="3"/>
+      <c r="W333" s="3"/>
+      <c r="X333" s="3"/>
+      <c r="Y333" s="3"/>
+    </row>
+    <row r="334" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -9048,8 +10448,12 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="3"/>
-    </row>
-    <row r="335" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V334" s="3"/>
+      <c r="W334" s="3"/>
+      <c r="X334" s="3"/>
+      <c r="Y334" s="3"/>
+    </row>
+    <row r="335" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -9069,8 +10473,12 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="3"/>
-    </row>
-    <row r="336" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V335" s="3"/>
+      <c r="W335" s="3"/>
+      <c r="X335" s="3"/>
+      <c r="Y335" s="3"/>
+    </row>
+    <row r="336" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -9090,8 +10498,12 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="3"/>
-    </row>
-    <row r="337" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V336" s="3"/>
+      <c r="W336" s="3"/>
+      <c r="X336" s="3"/>
+      <c r="Y336" s="3"/>
+    </row>
+    <row r="337" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -9111,8 +10523,12 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="3"/>
-    </row>
-    <row r="338" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V337" s="3"/>
+      <c r="W337" s="3"/>
+      <c r="X337" s="3"/>
+      <c r="Y337" s="3"/>
+    </row>
+    <row r="338" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -9132,8 +10548,12 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="3"/>
-    </row>
-    <row r="339" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V338" s="3"/>
+      <c r="W338" s="3"/>
+      <c r="X338" s="3"/>
+      <c r="Y338" s="3"/>
+    </row>
+    <row r="339" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -9153,8 +10573,12 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="3"/>
-    </row>
-    <row r="340" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V339" s="3"/>
+      <c r="W339" s="3"/>
+      <c r="X339" s="3"/>
+      <c r="Y339" s="3"/>
+    </row>
+    <row r="340" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -9174,8 +10598,12 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="3"/>
-    </row>
-    <row r="341" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V340" s="3"/>
+      <c r="W340" s="3"/>
+      <c r="X340" s="3"/>
+      <c r="Y340" s="3"/>
+    </row>
+    <row r="341" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -9195,8 +10623,12 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="3"/>
-    </row>
-    <row r="342" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V341" s="3"/>
+      <c r="W341" s="3"/>
+      <c r="X341" s="3"/>
+      <c r="Y341" s="3"/>
+    </row>
+    <row r="342" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -9216,8 +10648,12 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="3"/>
-    </row>
-    <row r="343" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V342" s="3"/>
+      <c r="W342" s="3"/>
+      <c r="X342" s="3"/>
+      <c r="Y342" s="3"/>
+    </row>
+    <row r="343" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -9237,8 +10673,12 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="3"/>
-    </row>
-    <row r="344" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V343" s="3"/>
+      <c r="W343" s="3"/>
+      <c r="X343" s="3"/>
+      <c r="Y343" s="3"/>
+    </row>
+    <row r="344" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -9258,8 +10698,12 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="3"/>
-    </row>
-    <row r="345" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V344" s="3"/>
+      <c r="W344" s="3"/>
+      <c r="X344" s="3"/>
+      <c r="Y344" s="3"/>
+    </row>
+    <row r="345" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -9279,8 +10723,12 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="3"/>
-    </row>
-    <row r="346" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V345" s="3"/>
+      <c r="W345" s="3"/>
+      <c r="X345" s="3"/>
+      <c r="Y345" s="3"/>
+    </row>
+    <row r="346" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -9300,8 +10748,12 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="3"/>
-    </row>
-    <row r="347" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V346" s="3"/>
+      <c r="W346" s="3"/>
+      <c r="X346" s="3"/>
+      <c r="Y346" s="3"/>
+    </row>
+    <row r="347" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -9321,8 +10773,12 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="3"/>
-    </row>
-    <row r="348" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V347" s="3"/>
+      <c r="W347" s="3"/>
+      <c r="X347" s="3"/>
+      <c r="Y347" s="3"/>
+    </row>
+    <row r="348" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -9342,8 +10798,12 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="3"/>
-    </row>
-    <row r="349" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V348" s="3"/>
+      <c r="W348" s="3"/>
+      <c r="X348" s="3"/>
+      <c r="Y348" s="3"/>
+    </row>
+    <row r="349" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="3"/>
@@ -9363,8 +10823,12 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="3"/>
-    </row>
-    <row r="350" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V349" s="3"/>
+      <c r="W349" s="3"/>
+      <c r="X349" s="3"/>
+      <c r="Y349" s="3"/>
+    </row>
+    <row r="350" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -9384,8 +10848,12 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="3"/>
-    </row>
-    <row r="351" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V350" s="3"/>
+      <c r="W350" s="3"/>
+      <c r="X350" s="3"/>
+      <c r="Y350" s="3"/>
+    </row>
+    <row r="351" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
@@ -9405,8 +10873,12 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="3"/>
-    </row>
-    <row r="352" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V351" s="3"/>
+      <c r="W351" s="3"/>
+      <c r="X351" s="3"/>
+      <c r="Y351" s="3"/>
+    </row>
+    <row r="352" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -9426,8 +10898,12 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="3"/>
-    </row>
-    <row r="353" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V352" s="3"/>
+      <c r="W352" s="3"/>
+      <c r="X352" s="3"/>
+      <c r="Y352" s="3"/>
+    </row>
+    <row r="353" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
       <c r="E353" s="3"/>
@@ -9447,8 +10923,12 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="3"/>
-    </row>
-    <row r="354" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V353" s="3"/>
+      <c r="W353" s="3"/>
+      <c r="X353" s="3"/>
+      <c r="Y353" s="3"/>
+    </row>
+    <row r="354" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -9468,8 +10948,12 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="3"/>
-    </row>
-    <row r="355" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V354" s="3"/>
+      <c r="W354" s="3"/>
+      <c r="X354" s="3"/>
+      <c r="Y354" s="3"/>
+    </row>
+    <row r="355" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C355" s="3"/>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -9489,8 +10973,12 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="3"/>
-    </row>
-    <row r="356" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V355" s="3"/>
+      <c r="W355" s="3"/>
+      <c r="X355" s="3"/>
+      <c r="Y355" s="3"/>
+    </row>
+    <row r="356" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
@@ -9510,8 +10998,12 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="3"/>
-    </row>
-    <row r="357" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V356" s="3"/>
+      <c r="W356" s="3"/>
+      <c r="X356" s="3"/>
+      <c r="Y356" s="3"/>
+    </row>
+    <row r="357" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
@@ -9531,8 +11023,12 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="3"/>
-    </row>
-    <row r="358" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V357" s="3"/>
+      <c r="W357" s="3"/>
+      <c r="X357" s="3"/>
+      <c r="Y357" s="3"/>
+    </row>
+    <row r="358" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -9552,8 +11048,12 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="3"/>
-    </row>
-    <row r="359" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V358" s="3"/>
+      <c r="W358" s="3"/>
+      <c r="X358" s="3"/>
+      <c r="Y358" s="3"/>
+    </row>
+    <row r="359" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
@@ -9573,8 +11073,12 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="3"/>
-    </row>
-    <row r="360" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V359" s="3"/>
+      <c r="W359" s="3"/>
+      <c r="X359" s="3"/>
+      <c r="Y359" s="3"/>
+    </row>
+    <row r="360" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -9594,8 +11098,12 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="3"/>
-    </row>
-    <row r="361" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V360" s="3"/>
+      <c r="W360" s="3"/>
+      <c r="X360" s="3"/>
+      <c r="Y360" s="3"/>
+    </row>
+    <row r="361" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
@@ -9615,8 +11123,12 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="3"/>
-    </row>
-    <row r="362" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V361" s="3"/>
+      <c r="W361" s="3"/>
+      <c r="X361" s="3"/>
+      <c r="Y361" s="3"/>
+    </row>
+    <row r="362" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -9636,8 +11148,12 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="3"/>
-    </row>
-    <row r="363" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V362" s="3"/>
+      <c r="W362" s="3"/>
+      <c r="X362" s="3"/>
+      <c r="Y362" s="3"/>
+    </row>
+    <row r="363" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C363" s="3"/>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
@@ -9657,8 +11173,12 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="3"/>
-    </row>
-    <row r="364" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V363" s="3"/>
+      <c r="W363" s="3"/>
+      <c r="X363" s="3"/>
+      <c r="Y363" s="3"/>
+    </row>
+    <row r="364" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -9678,8 +11198,12 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="3"/>
-    </row>
-    <row r="365" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V364" s="3"/>
+      <c r="W364" s="3"/>
+      <c r="X364" s="3"/>
+      <c r="Y364" s="3"/>
+    </row>
+    <row r="365" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
@@ -9699,8 +11223,12 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="3"/>
-    </row>
-    <row r="366" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V365" s="3"/>
+      <c r="W365" s="3"/>
+      <c r="X365" s="3"/>
+      <c r="Y365" s="3"/>
+    </row>
+    <row r="366" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -9720,8 +11248,12 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="3"/>
-    </row>
-    <row r="367" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V366" s="3"/>
+      <c r="W366" s="3"/>
+      <c r="X366" s="3"/>
+      <c r="Y366" s="3"/>
+    </row>
+    <row r="367" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
@@ -9741,8 +11273,12 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="3"/>
-    </row>
-    <row r="368" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V367" s="3"/>
+      <c r="W367" s="3"/>
+      <c r="X367" s="3"/>
+      <c r="Y367" s="3"/>
+    </row>
+    <row r="368" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -9762,8 +11298,12 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="3"/>
-    </row>
-    <row r="369" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V368" s="3"/>
+      <c r="W368" s="3"/>
+      <c r="X368" s="3"/>
+      <c r="Y368" s="3"/>
+    </row>
+    <row r="369" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
@@ -9783,8 +11323,12 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="3"/>
-    </row>
-    <row r="370" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V369" s="3"/>
+      <c r="W369" s="3"/>
+      <c r="X369" s="3"/>
+      <c r="Y369" s="3"/>
+    </row>
+    <row r="370" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -9804,8 +11348,12 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="3"/>
-    </row>
-    <row r="371" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V370" s="3"/>
+      <c r="W370" s="3"/>
+      <c r="X370" s="3"/>
+      <c r="Y370" s="3"/>
+    </row>
+    <row r="371" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
@@ -9825,8 +11373,12 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="3"/>
-    </row>
-    <row r="372" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V371" s="3"/>
+      <c r="W371" s="3"/>
+      <c r="X371" s="3"/>
+      <c r="Y371" s="3"/>
+    </row>
+    <row r="372" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -9846,8 +11398,12 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="3"/>
-    </row>
-    <row r="373" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V372" s="3"/>
+      <c r="W372" s="3"/>
+      <c r="X372" s="3"/>
+      <c r="Y372" s="3"/>
+    </row>
+    <row r="373" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
@@ -9867,8 +11423,12 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="3"/>
-    </row>
-    <row r="374" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V373" s="3"/>
+      <c r="W373" s="3"/>
+      <c r="X373" s="3"/>
+      <c r="Y373" s="3"/>
+    </row>
+    <row r="374" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -9888,8 +11448,12 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="3"/>
-    </row>
-    <row r="375" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V374" s="3"/>
+      <c r="W374" s="3"/>
+      <c r="X374" s="3"/>
+      <c r="Y374" s="3"/>
+    </row>
+    <row r="375" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
@@ -9909,8 +11473,12 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="3"/>
-    </row>
-    <row r="376" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V375" s="3"/>
+      <c r="W375" s="3"/>
+      <c r="X375" s="3"/>
+      <c r="Y375" s="3"/>
+    </row>
+    <row r="376" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -9930,8 +11498,12 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="3"/>
-    </row>
-    <row r="377" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V376" s="3"/>
+      <c r="W376" s="3"/>
+      <c r="X376" s="3"/>
+      <c r="Y376" s="3"/>
+    </row>
+    <row r="377" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
@@ -9951,8 +11523,12 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="3"/>
-    </row>
-    <row r="378" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V377" s="3"/>
+      <c r="W377" s="3"/>
+      <c r="X377" s="3"/>
+      <c r="Y377" s="3"/>
+    </row>
+    <row r="378" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -9972,8 +11548,12 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="3"/>
-    </row>
-    <row r="379" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V378" s="3"/>
+      <c r="W378" s="3"/>
+      <c r="X378" s="3"/>
+      <c r="Y378" s="3"/>
+    </row>
+    <row r="379" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
@@ -9993,8 +11573,12 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="3"/>
-    </row>
-    <row r="380" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V379" s="3"/>
+      <c r="W379" s="3"/>
+      <c r="X379" s="3"/>
+      <c r="Y379" s="3"/>
+    </row>
+    <row r="380" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -10014,8 +11598,12 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="3"/>
-    </row>
-    <row r="381" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V380" s="3"/>
+      <c r="W380" s="3"/>
+      <c r="X380" s="3"/>
+      <c r="Y380" s="3"/>
+    </row>
+    <row r="381" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
@@ -10035,8 +11623,12 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="3"/>
-    </row>
-    <row r="382" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V381" s="3"/>
+      <c r="W381" s="3"/>
+      <c r="X381" s="3"/>
+      <c r="Y381" s="3"/>
+    </row>
+    <row r="382" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -10056,8 +11648,12 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="3"/>
-    </row>
-    <row r="383" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V382" s="3"/>
+      <c r="W382" s="3"/>
+      <c r="X382" s="3"/>
+      <c r="Y382" s="3"/>
+    </row>
+    <row r="383" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
@@ -10077,8 +11673,12 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="3"/>
-    </row>
-    <row r="384" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V383" s="3"/>
+      <c r="W383" s="3"/>
+      <c r="X383" s="3"/>
+      <c r="Y383" s="3"/>
+    </row>
+    <row r="384" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -10098,8 +11698,12 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="3"/>
-    </row>
-    <row r="385" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V384" s="3"/>
+      <c r="W384" s="3"/>
+      <c r="X384" s="3"/>
+      <c r="Y384" s="3"/>
+    </row>
+    <row r="385" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
@@ -10119,8 +11723,12 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="3"/>
-    </row>
-    <row r="386" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V385" s="3"/>
+      <c r="W385" s="3"/>
+      <c r="X385" s="3"/>
+      <c r="Y385" s="3"/>
+    </row>
+    <row r="386" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -10140,8 +11748,12 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="3"/>
-    </row>
-    <row r="387" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V386" s="3"/>
+      <c r="W386" s="3"/>
+      <c r="X386" s="3"/>
+      <c r="Y386" s="3"/>
+    </row>
+    <row r="387" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
@@ -10161,8 +11773,12 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="3"/>
-    </row>
-    <row r="388" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V387" s="3"/>
+      <c r="W387" s="3"/>
+      <c r="X387" s="3"/>
+      <c r="Y387" s="3"/>
+    </row>
+    <row r="388" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -10182,8 +11798,12 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="3"/>
-    </row>
-    <row r="389" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V388" s="3"/>
+      <c r="W388" s="3"/>
+      <c r="X388" s="3"/>
+      <c r="Y388" s="3"/>
+    </row>
+    <row r="389" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
@@ -10203,8 +11823,12 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="3"/>
-    </row>
-    <row r="390" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V389" s="3"/>
+      <c r="W389" s="3"/>
+      <c r="X389" s="3"/>
+      <c r="Y389" s="3"/>
+    </row>
+    <row r="390" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -10224,8 +11848,12 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="3"/>
-    </row>
-    <row r="391" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V390" s="3"/>
+      <c r="W390" s="3"/>
+      <c r="X390" s="3"/>
+      <c r="Y390" s="3"/>
+    </row>
+    <row r="391" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
@@ -10245,8 +11873,12 @@
       <c r="S391" s="3"/>
       <c r="T391" s="3"/>
       <c r="U391" s="3"/>
-    </row>
-    <row r="392" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V391" s="3"/>
+      <c r="W391" s="3"/>
+      <c r="X391" s="3"/>
+      <c r="Y391" s="3"/>
+    </row>
+    <row r="392" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -10266,8 +11898,12 @@
       <c r="S392" s="3"/>
       <c r="T392" s="3"/>
       <c r="U392" s="3"/>
-    </row>
-    <row r="393" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V392" s="3"/>
+      <c r="W392" s="3"/>
+      <c r="X392" s="3"/>
+      <c r="Y392" s="3"/>
+    </row>
+    <row r="393" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
@@ -10287,8 +11923,12 @@
       <c r="S393" s="3"/>
       <c r="T393" s="3"/>
       <c r="U393" s="3"/>
-    </row>
-    <row r="394" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V393" s="3"/>
+      <c r="W393" s="3"/>
+      <c r="X393" s="3"/>
+      <c r="Y393" s="3"/>
+    </row>
+    <row r="394" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -10308,8 +11948,12 @@
       <c r="S394" s="3"/>
       <c r="T394" s="3"/>
       <c r="U394" s="3"/>
-    </row>
-    <row r="395" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V394" s="3"/>
+      <c r="W394" s="3"/>
+      <c r="X394" s="3"/>
+      <c r="Y394" s="3"/>
+    </row>
+    <row r="395" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
@@ -10329,8 +11973,12 @@
       <c r="S395" s="3"/>
       <c r="T395" s="3"/>
       <c r="U395" s="3"/>
-    </row>
-    <row r="396" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V395" s="3"/>
+      <c r="W395" s="3"/>
+      <c r="X395" s="3"/>
+      <c r="Y395" s="3"/>
+    </row>
+    <row r="396" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -10350,8 +11998,12 @@
       <c r="S396" s="3"/>
       <c r="T396" s="3"/>
       <c r="U396" s="3"/>
-    </row>
-    <row r="397" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V396" s="3"/>
+      <c r="W396" s="3"/>
+      <c r="X396" s="3"/>
+      <c r="Y396" s="3"/>
+    </row>
+    <row r="397" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
@@ -10371,8 +12023,12 @@
       <c r="S397" s="3"/>
       <c r="T397" s="3"/>
       <c r="U397" s="3"/>
-    </row>
-    <row r="398" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V397" s="3"/>
+      <c r="W397" s="3"/>
+      <c r="X397" s="3"/>
+      <c r="Y397" s="3"/>
+    </row>
+    <row r="398" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -10392,8 +12048,12 @@
       <c r="S398" s="3"/>
       <c r="T398" s="3"/>
       <c r="U398" s="3"/>
-    </row>
-    <row r="399" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V398" s="3"/>
+      <c r="W398" s="3"/>
+      <c r="X398" s="3"/>
+      <c r="Y398" s="3"/>
+    </row>
+    <row r="399" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
@@ -10413,8 +12073,12 @@
       <c r="S399" s="3"/>
       <c r="T399" s="3"/>
       <c r="U399" s="3"/>
-    </row>
-    <row r="400" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V399" s="3"/>
+      <c r="W399" s="3"/>
+      <c r="X399" s="3"/>
+      <c r="Y399" s="3"/>
+    </row>
+    <row r="400" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -10434,8 +12098,12 @@
       <c r="S400" s="3"/>
       <c r="T400" s="3"/>
       <c r="U400" s="3"/>
-    </row>
-    <row r="401" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V400" s="3"/>
+      <c r="W400" s="3"/>
+      <c r="X400" s="3"/>
+      <c r="Y400" s="3"/>
+    </row>
+    <row r="401" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
@@ -10455,8 +12123,12 @@
       <c r="S401" s="3"/>
       <c r="T401" s="3"/>
       <c r="U401" s="3"/>
-    </row>
-    <row r="402" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V401" s="3"/>
+      <c r="W401" s="3"/>
+      <c r="X401" s="3"/>
+      <c r="Y401" s="3"/>
+    </row>
+    <row r="402" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -10476,8 +12148,12 @@
       <c r="S402" s="3"/>
       <c r="T402" s="3"/>
       <c r="U402" s="3"/>
-    </row>
-    <row r="403" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V402" s="3"/>
+      <c r="W402" s="3"/>
+      <c r="X402" s="3"/>
+      <c r="Y402" s="3"/>
+    </row>
+    <row r="403" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
       <c r="E403" s="3"/>
@@ -10497,8 +12173,12 @@
       <c r="S403" s="3"/>
       <c r="T403" s="3"/>
       <c r="U403" s="3"/>
-    </row>
-    <row r="404" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V403" s="3"/>
+      <c r="W403" s="3"/>
+      <c r="X403" s="3"/>
+      <c r="Y403" s="3"/>
+    </row>
+    <row r="404" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C404" s="3"/>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
@@ -10518,8 +12198,12 @@
       <c r="S404" s="3"/>
       <c r="T404" s="3"/>
       <c r="U404" s="3"/>
-    </row>
-    <row r="405" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V404" s="3"/>
+      <c r="W404" s="3"/>
+      <c r="X404" s="3"/>
+      <c r="Y404" s="3"/>
+    </row>
+    <row r="405" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C405" s="3"/>
       <c r="D405" s="3"/>
       <c r="E405" s="3"/>
@@ -10539,8 +12223,12 @@
       <c r="S405" s="3"/>
       <c r="T405" s="3"/>
       <c r="U405" s="3"/>
-    </row>
-    <row r="406" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V405" s="3"/>
+      <c r="W405" s="3"/>
+      <c r="X405" s="3"/>
+      <c r="Y405" s="3"/>
+    </row>
+    <row r="406" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C406" s="3"/>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
@@ -10560,8 +12248,12 @@
       <c r="S406" s="3"/>
       <c r="T406" s="3"/>
       <c r="U406" s="3"/>
-    </row>
-    <row r="407" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V406" s="3"/>
+      <c r="W406" s="3"/>
+      <c r="X406" s="3"/>
+      <c r="Y406" s="3"/>
+    </row>
+    <row r="407" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C407" s="3"/>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
@@ -10581,8 +12273,12 @@
       <c r="S407" s="3"/>
       <c r="T407" s="3"/>
       <c r="U407" s="3"/>
-    </row>
-    <row r="408" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V407" s="3"/>
+      <c r="W407" s="3"/>
+      <c r="X407" s="3"/>
+      <c r="Y407" s="3"/>
+    </row>
+    <row r="408" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C408" s="3"/>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
@@ -10602,8 +12298,12 @@
       <c r="S408" s="3"/>
       <c r="T408" s="3"/>
       <c r="U408" s="3"/>
-    </row>
-    <row r="409" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V408" s="3"/>
+      <c r="W408" s="3"/>
+      <c r="X408" s="3"/>
+      <c r="Y408" s="3"/>
+    </row>
+    <row r="409" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C409" s="3"/>
       <c r="D409" s="3"/>
       <c r="E409" s="3"/>
@@ -10623,8 +12323,12 @@
       <c r="S409" s="3"/>
       <c r="T409" s="3"/>
       <c r="U409" s="3"/>
-    </row>
-    <row r="410" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V409" s="3"/>
+      <c r="W409" s="3"/>
+      <c r="X409" s="3"/>
+      <c r="Y409" s="3"/>
+    </row>
+    <row r="410" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C410" s="3"/>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
@@ -10644,8 +12348,12 @@
       <c r="S410" s="3"/>
       <c r="T410" s="3"/>
       <c r="U410" s="3"/>
-    </row>
-    <row r="411" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V410" s="3"/>
+      <c r="W410" s="3"/>
+      <c r="X410" s="3"/>
+      <c r="Y410" s="3"/>
+    </row>
+    <row r="411" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C411" s="3"/>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
@@ -10665,8 +12373,12 @@
       <c r="S411" s="3"/>
       <c r="T411" s="3"/>
       <c r="U411" s="3"/>
-    </row>
-    <row r="412" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V411" s="3"/>
+      <c r="W411" s="3"/>
+      <c r="X411" s="3"/>
+      <c r="Y411" s="3"/>
+    </row>
+    <row r="412" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C412" s="3"/>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
@@ -10686,8 +12398,12 @@
       <c r="S412" s="3"/>
       <c r="T412" s="3"/>
       <c r="U412" s="3"/>
-    </row>
-    <row r="413" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V412" s="3"/>
+      <c r="W412" s="3"/>
+      <c r="X412" s="3"/>
+      <c r="Y412" s="3"/>
+    </row>
+    <row r="413" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C413" s="3"/>
       <c r="D413" s="3"/>
       <c r="E413" s="3"/>
@@ -10707,8 +12423,12 @@
       <c r="S413" s="3"/>
       <c r="T413" s="3"/>
       <c r="U413" s="3"/>
-    </row>
-    <row r="414" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V413" s="3"/>
+      <c r="W413" s="3"/>
+      <c r="X413" s="3"/>
+      <c r="Y413" s="3"/>
+    </row>
+    <row r="414" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C414" s="3"/>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -10728,8 +12448,12 @@
       <c r="S414" s="3"/>
       <c r="T414" s="3"/>
       <c r="U414" s="3"/>
-    </row>
-    <row r="415" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V414" s="3"/>
+      <c r="W414" s="3"/>
+      <c r="X414" s="3"/>
+      <c r="Y414" s="3"/>
+    </row>
+    <row r="415" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C415" s="3"/>
       <c r="D415" s="3"/>
       <c r="E415" s="3"/>
@@ -10749,8 +12473,12 @@
       <c r="S415" s="3"/>
       <c r="T415" s="3"/>
       <c r="U415" s="3"/>
-    </row>
-    <row r="416" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V415" s="3"/>
+      <c r="W415" s="3"/>
+      <c r="X415" s="3"/>
+      <c r="Y415" s="3"/>
+    </row>
+    <row r="416" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C416" s="3"/>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
@@ -10770,8 +12498,12 @@
       <c r="S416" s="3"/>
       <c r="T416" s="3"/>
       <c r="U416" s="3"/>
-    </row>
-    <row r="417" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V416" s="3"/>
+      <c r="W416" s="3"/>
+      <c r="X416" s="3"/>
+      <c r="Y416" s="3"/>
+    </row>
+    <row r="417" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C417" s="3"/>
       <c r="D417" s="3"/>
       <c r="E417" s="3"/>
@@ -10791,8 +12523,12 @@
       <c r="S417" s="3"/>
       <c r="T417" s="3"/>
       <c r="U417" s="3"/>
-    </row>
-    <row r="418" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V417" s="3"/>
+      <c r="W417" s="3"/>
+      <c r="X417" s="3"/>
+      <c r="Y417" s="3"/>
+    </row>
+    <row r="418" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C418" s="3"/>
       <c r="D418" s="3"/>
       <c r="E418" s="3"/>
@@ -10812,8 +12548,12 @@
       <c r="S418" s="3"/>
       <c r="T418" s="3"/>
       <c r="U418" s="3"/>
-    </row>
-    <row r="419" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V418" s="3"/>
+      <c r="W418" s="3"/>
+      <c r="X418" s="3"/>
+      <c r="Y418" s="3"/>
+    </row>
+    <row r="419" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C419" s="3"/>
       <c r="D419" s="3"/>
       <c r="E419" s="3"/>
@@ -10833,8 +12573,12 @@
       <c r="S419" s="3"/>
       <c r="T419" s="3"/>
       <c r="U419" s="3"/>
-    </row>
-    <row r="420" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V419" s="3"/>
+      <c r="W419" s="3"/>
+      <c r="X419" s="3"/>
+      <c r="Y419" s="3"/>
+    </row>
+    <row r="420" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C420" s="3"/>
       <c r="D420" s="3"/>
       <c r="E420" s="3"/>
@@ -10854,8 +12598,12 @@
       <c r="S420" s="3"/>
       <c r="T420" s="3"/>
       <c r="U420" s="3"/>
-    </row>
-    <row r="421" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V420" s="3"/>
+      <c r="W420" s="3"/>
+      <c r="X420" s="3"/>
+      <c r="Y420" s="3"/>
+    </row>
+    <row r="421" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C421" s="3"/>
       <c r="D421" s="3"/>
       <c r="E421" s="3"/>
@@ -10875,8 +12623,12 @@
       <c r="S421" s="3"/>
       <c r="T421" s="3"/>
       <c r="U421" s="3"/>
-    </row>
-    <row r="422" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V421" s="3"/>
+      <c r="W421" s="3"/>
+      <c r="X421" s="3"/>
+      <c r="Y421" s="3"/>
+    </row>
+    <row r="422" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C422" s="3"/>
       <c r="D422" s="3"/>
       <c r="E422" s="3"/>
@@ -10896,8 +12648,12 @@
       <c r="S422" s="3"/>
       <c r="T422" s="3"/>
       <c r="U422" s="3"/>
-    </row>
-    <row r="423" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V422" s="3"/>
+      <c r="W422" s="3"/>
+      <c r="X422" s="3"/>
+      <c r="Y422" s="3"/>
+    </row>
+    <row r="423" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C423" s="3"/>
       <c r="D423" s="3"/>
       <c r="E423" s="3"/>
@@ -10917,8 +12673,12 @@
       <c r="S423" s="3"/>
       <c r="T423" s="3"/>
       <c r="U423" s="3"/>
-    </row>
-    <row r="424" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V423" s="3"/>
+      <c r="W423" s="3"/>
+      <c r="X423" s="3"/>
+      <c r="Y423" s="3"/>
+    </row>
+    <row r="424" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C424" s="3"/>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
@@ -10938,8 +12698,12 @@
       <c r="S424" s="3"/>
       <c r="T424" s="3"/>
       <c r="U424" s="3"/>
-    </row>
-    <row r="425" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V424" s="3"/>
+      <c r="W424" s="3"/>
+      <c r="X424" s="3"/>
+      <c r="Y424" s="3"/>
+    </row>
+    <row r="425" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C425" s="3"/>
       <c r="D425" s="3"/>
       <c r="E425" s="3"/>
@@ -10959,8 +12723,12 @@
       <c r="S425" s="3"/>
       <c r="T425" s="3"/>
       <c r="U425" s="3"/>
-    </row>
-    <row r="426" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V425" s="3"/>
+      <c r="W425" s="3"/>
+      <c r="X425" s="3"/>
+      <c r="Y425" s="3"/>
+    </row>
+    <row r="426" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C426" s="3"/>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
@@ -10980,8 +12748,12 @@
       <c r="S426" s="3"/>
       <c r="T426" s="3"/>
       <c r="U426" s="3"/>
-    </row>
-    <row r="427" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V426" s="3"/>
+      <c r="W426" s="3"/>
+      <c r="X426" s="3"/>
+      <c r="Y426" s="3"/>
+    </row>
+    <row r="427" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C427" s="3"/>
       <c r="D427" s="3"/>
       <c r="E427" s="3"/>
@@ -11001,8 +12773,12 @@
       <c r="S427" s="3"/>
       <c r="T427" s="3"/>
       <c r="U427" s="3"/>
-    </row>
-    <row r="428" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V427" s="3"/>
+      <c r="W427" s="3"/>
+      <c r="X427" s="3"/>
+      <c r="Y427" s="3"/>
+    </row>
+    <row r="428" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C428" s="3"/>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
@@ -11022,8 +12798,12 @@
       <c r="S428" s="3"/>
       <c r="T428" s="3"/>
       <c r="U428" s="3"/>
-    </row>
-    <row r="429" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V428" s="3"/>
+      <c r="W428" s="3"/>
+      <c r="X428" s="3"/>
+      <c r="Y428" s="3"/>
+    </row>
+    <row r="429" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C429" s="3"/>
       <c r="D429" s="3"/>
       <c r="E429" s="3"/>
@@ -11043,8 +12823,12 @@
       <c r="S429" s="3"/>
       <c r="T429" s="3"/>
       <c r="U429" s="3"/>
-    </row>
-    <row r="430" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V429" s="3"/>
+      <c r="W429" s="3"/>
+      <c r="X429" s="3"/>
+      <c r="Y429" s="3"/>
+    </row>
+    <row r="430" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C430" s="3"/>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
@@ -11064,8 +12848,12 @@
       <c r="S430" s="3"/>
       <c r="T430" s="3"/>
       <c r="U430" s="3"/>
-    </row>
-    <row r="431" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V430" s="3"/>
+      <c r="W430" s="3"/>
+      <c r="X430" s="3"/>
+      <c r="Y430" s="3"/>
+    </row>
+    <row r="431" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C431" s="3"/>
       <c r="D431" s="3"/>
       <c r="E431" s="3"/>
@@ -11085,8 +12873,12 @@
       <c r="S431" s="3"/>
       <c r="T431" s="3"/>
       <c r="U431" s="3"/>
-    </row>
-    <row r="432" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V431" s="3"/>
+      <c r="W431" s="3"/>
+      <c r="X431" s="3"/>
+      <c r="Y431" s="3"/>
+    </row>
+    <row r="432" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C432" s="3"/>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
@@ -11106,8 +12898,12 @@
       <c r="S432" s="3"/>
       <c r="T432" s="3"/>
       <c r="U432" s="3"/>
-    </row>
-    <row r="433" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V432" s="3"/>
+      <c r="W432" s="3"/>
+      <c r="X432" s="3"/>
+      <c r="Y432" s="3"/>
+    </row>
+    <row r="433" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C433" s="3"/>
       <c r="D433" s="3"/>
       <c r="E433" s="3"/>
@@ -11127,8 +12923,12 @@
       <c r="S433" s="3"/>
       <c r="T433" s="3"/>
       <c r="U433" s="3"/>
-    </row>
-    <row r="434" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V433" s="3"/>
+      <c r="W433" s="3"/>
+      <c r="X433" s="3"/>
+      <c r="Y433" s="3"/>
+    </row>
+    <row r="434" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C434" s="3"/>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
@@ -11148,8 +12948,12 @@
       <c r="S434" s="3"/>
       <c r="T434" s="3"/>
       <c r="U434" s="3"/>
-    </row>
-    <row r="435" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V434" s="3"/>
+      <c r="W434" s="3"/>
+      <c r="X434" s="3"/>
+      <c r="Y434" s="3"/>
+    </row>
+    <row r="435" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C435" s="3"/>
       <c r="D435" s="3"/>
       <c r="E435" s="3"/>
@@ -11169,8 +12973,12 @@
       <c r="S435" s="3"/>
       <c r="T435" s="3"/>
       <c r="U435" s="3"/>
-    </row>
-    <row r="436" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V435" s="3"/>
+      <c r="W435" s="3"/>
+      <c r="X435" s="3"/>
+      <c r="Y435" s="3"/>
+    </row>
+    <row r="436" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C436" s="3"/>
       <c r="D436" s="3"/>
       <c r="E436" s="3"/>
@@ -11190,8 +12998,12 @@
       <c r="S436" s="3"/>
       <c r="T436" s="3"/>
       <c r="U436" s="3"/>
-    </row>
-    <row r="437" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V436" s="3"/>
+      <c r="W436" s="3"/>
+      <c r="X436" s="3"/>
+      <c r="Y436" s="3"/>
+    </row>
+    <row r="437" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C437" s="3"/>
       <c r="D437" s="3"/>
       <c r="E437" s="3"/>
@@ -11211,8 +13023,12 @@
       <c r="S437" s="3"/>
       <c r="T437" s="3"/>
       <c r="U437" s="3"/>
-    </row>
-    <row r="438" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V437" s="3"/>
+      <c r="W437" s="3"/>
+      <c r="X437" s="3"/>
+      <c r="Y437" s="3"/>
+    </row>
+    <row r="438" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C438" s="3"/>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
@@ -11232,8 +13048,12 @@
       <c r="S438" s="3"/>
       <c r="T438" s="3"/>
       <c r="U438" s="3"/>
-    </row>
-    <row r="439" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V438" s="3"/>
+      <c r="W438" s="3"/>
+      <c r="X438" s="3"/>
+      <c r="Y438" s="3"/>
+    </row>
+    <row r="439" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C439" s="3"/>
       <c r="D439" s="3"/>
       <c r="E439" s="3"/>
@@ -11253,8 +13073,12 @@
       <c r="S439" s="3"/>
       <c r="T439" s="3"/>
       <c r="U439" s="3"/>
-    </row>
-    <row r="440" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V439" s="3"/>
+      <c r="W439" s="3"/>
+      <c r="X439" s="3"/>
+      <c r="Y439" s="3"/>
+    </row>
+    <row r="440" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C440" s="3"/>
       <c r="D440" s="3"/>
       <c r="E440" s="3"/>
@@ -11274,8 +13098,12 @@
       <c r="S440" s="3"/>
       <c r="T440" s="3"/>
       <c r="U440" s="3"/>
-    </row>
-    <row r="441" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V440" s="3"/>
+      <c r="W440" s="3"/>
+      <c r="X440" s="3"/>
+      <c r="Y440" s="3"/>
+    </row>
+    <row r="441" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C441" s="3"/>
       <c r="D441" s="3"/>
       <c r="E441" s="3"/>
@@ -11295,8 +13123,12 @@
       <c r="S441" s="3"/>
       <c r="T441" s="3"/>
       <c r="U441" s="3"/>
-    </row>
-    <row r="442" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V441" s="3"/>
+      <c r="W441" s="3"/>
+      <c r="X441" s="3"/>
+      <c r="Y441" s="3"/>
+    </row>
+    <row r="442" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C442" s="3"/>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
@@ -11316,8 +13148,12 @@
       <c r="S442" s="3"/>
       <c r="T442" s="3"/>
       <c r="U442" s="3"/>
-    </row>
-    <row r="443" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V442" s="3"/>
+      <c r="W442" s="3"/>
+      <c r="X442" s="3"/>
+      <c r="Y442" s="3"/>
+    </row>
+    <row r="443" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C443" s="3"/>
       <c r="D443" s="3"/>
       <c r="E443" s="3"/>
@@ -11337,8 +13173,12 @@
       <c r="S443" s="3"/>
       <c r="T443" s="3"/>
       <c r="U443" s="3"/>
-    </row>
-    <row r="444" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V443" s="3"/>
+      <c r="W443" s="3"/>
+      <c r="X443" s="3"/>
+      <c r="Y443" s="3"/>
+    </row>
+    <row r="444" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C444" s="3"/>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
@@ -11358,8 +13198,12 @@
       <c r="S444" s="3"/>
       <c r="T444" s="3"/>
       <c r="U444" s="3"/>
-    </row>
-    <row r="445" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V444" s="3"/>
+      <c r="W444" s="3"/>
+      <c r="X444" s="3"/>
+      <c r="Y444" s="3"/>
+    </row>
+    <row r="445" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C445" s="3"/>
       <c r="D445" s="3"/>
       <c r="E445" s="3"/>
@@ -11379,8 +13223,12 @@
       <c r="S445" s="3"/>
       <c r="T445" s="3"/>
       <c r="U445" s="3"/>
-    </row>
-    <row r="446" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V445" s="3"/>
+      <c r="W445" s="3"/>
+      <c r="X445" s="3"/>
+      <c r="Y445" s="3"/>
+    </row>
+    <row r="446" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C446" s="3"/>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
@@ -11400,8 +13248,12 @@
       <c r="S446" s="3"/>
       <c r="T446" s="3"/>
       <c r="U446" s="3"/>
-    </row>
-    <row r="447" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V446" s="3"/>
+      <c r="W446" s="3"/>
+      <c r="X446" s="3"/>
+      <c r="Y446" s="3"/>
+    </row>
+    <row r="447" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C447" s="3"/>
       <c r="D447" s="3"/>
       <c r="E447" s="3"/>
@@ -11421,8 +13273,12 @@
       <c r="S447" s="3"/>
       <c r="T447" s="3"/>
       <c r="U447" s="3"/>
-    </row>
-    <row r="448" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V447" s="3"/>
+      <c r="W447" s="3"/>
+      <c r="X447" s="3"/>
+      <c r="Y447" s="3"/>
+    </row>
+    <row r="448" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C448" s="3"/>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
@@ -11442,8 +13298,12 @@
       <c r="S448" s="3"/>
       <c r="T448" s="3"/>
       <c r="U448" s="3"/>
-    </row>
-    <row r="449" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V448" s="3"/>
+      <c r="W448" s="3"/>
+      <c r="X448" s="3"/>
+      <c r="Y448" s="3"/>
+    </row>
+    <row r="449" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C449" s="3"/>
       <c r="D449" s="3"/>
       <c r="E449" s="3"/>
@@ -11463,8 +13323,12 @@
       <c r="S449" s="3"/>
       <c r="T449" s="3"/>
       <c r="U449" s="3"/>
-    </row>
-    <row r="450" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V449" s="3"/>
+      <c r="W449" s="3"/>
+      <c r="X449" s="3"/>
+      <c r="Y449" s="3"/>
+    </row>
+    <row r="450" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C450" s="3"/>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
@@ -11484,8 +13348,12 @@
       <c r="S450" s="3"/>
       <c r="T450" s="3"/>
       <c r="U450" s="3"/>
-    </row>
-    <row r="451" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V450" s="3"/>
+      <c r="W450" s="3"/>
+      <c r="X450" s="3"/>
+      <c r="Y450" s="3"/>
+    </row>
+    <row r="451" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C451" s="3"/>
       <c r="D451" s="3"/>
       <c r="E451" s="3"/>
@@ -11505,8 +13373,12 @@
       <c r="S451" s="3"/>
       <c r="T451" s="3"/>
       <c r="U451" s="3"/>
-    </row>
-    <row r="452" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V451" s="3"/>
+      <c r="W451" s="3"/>
+      <c r="X451" s="3"/>
+      <c r="Y451" s="3"/>
+    </row>
+    <row r="452" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C452" s="3"/>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
@@ -11526,8 +13398,12 @@
       <c r="S452" s="3"/>
       <c r="T452" s="3"/>
       <c r="U452" s="3"/>
-    </row>
-    <row r="453" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V452" s="3"/>
+      <c r="W452" s="3"/>
+      <c r="X452" s="3"/>
+      <c r="Y452" s="3"/>
+    </row>
+    <row r="453" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C453" s="3"/>
       <c r="D453" s="3"/>
       <c r="E453" s="3"/>
@@ -11547,8 +13423,12 @@
       <c r="S453" s="3"/>
       <c r="T453" s="3"/>
       <c r="U453" s="3"/>
-    </row>
-    <row r="454" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V453" s="3"/>
+      <c r="W453" s="3"/>
+      <c r="X453" s="3"/>
+      <c r="Y453" s="3"/>
+    </row>
+    <row r="454" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C454" s="3"/>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
@@ -11568,8 +13448,12 @@
       <c r="S454" s="3"/>
       <c r="T454" s="3"/>
       <c r="U454" s="3"/>
-    </row>
-    <row r="455" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V454" s="3"/>
+      <c r="W454" s="3"/>
+      <c r="X454" s="3"/>
+      <c r="Y454" s="3"/>
+    </row>
+    <row r="455" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C455" s="3"/>
       <c r="D455" s="3"/>
       <c r="E455" s="3"/>
@@ -11589,8 +13473,12 @@
       <c r="S455" s="3"/>
       <c r="T455" s="3"/>
       <c r="U455" s="3"/>
-    </row>
-    <row r="456" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V455" s="3"/>
+      <c r="W455" s="3"/>
+      <c r="X455" s="3"/>
+      <c r="Y455" s="3"/>
+    </row>
+    <row r="456" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C456" s="3"/>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
@@ -11610,8 +13498,12 @@
       <c r="S456" s="3"/>
       <c r="T456" s="3"/>
       <c r="U456" s="3"/>
-    </row>
-    <row r="457" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V456" s="3"/>
+      <c r="W456" s="3"/>
+      <c r="X456" s="3"/>
+      <c r="Y456" s="3"/>
+    </row>
+    <row r="457" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C457" s="3"/>
       <c r="D457" s="3"/>
       <c r="E457" s="3"/>
@@ -11631,8 +13523,12 @@
       <c r="S457" s="3"/>
       <c r="T457" s="3"/>
       <c r="U457" s="3"/>
-    </row>
-    <row r="458" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V457" s="3"/>
+      <c r="W457" s="3"/>
+      <c r="X457" s="3"/>
+      <c r="Y457" s="3"/>
+    </row>
+    <row r="458" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C458" s="3"/>
       <c r="D458" s="3"/>
       <c r="E458" s="3"/>
@@ -11652,8 +13548,12 @@
       <c r="S458" s="3"/>
       <c r="T458" s="3"/>
       <c r="U458" s="3"/>
-    </row>
-    <row r="459" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V458" s="3"/>
+      <c r="W458" s="3"/>
+      <c r="X458" s="3"/>
+      <c r="Y458" s="3"/>
+    </row>
+    <row r="459" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C459" s="3"/>
       <c r="D459" s="3"/>
       <c r="E459" s="3"/>
@@ -11673,8 +13573,12 @@
       <c r="S459" s="3"/>
       <c r="T459" s="3"/>
       <c r="U459" s="3"/>
-    </row>
-    <row r="460" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V459" s="3"/>
+      <c r="W459" s="3"/>
+      <c r="X459" s="3"/>
+      <c r="Y459" s="3"/>
+    </row>
+    <row r="460" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C460" s="3"/>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
@@ -11694,8 +13598,12 @@
       <c r="S460" s="3"/>
       <c r="T460" s="3"/>
       <c r="U460" s="3"/>
-    </row>
-    <row r="461" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V460" s="3"/>
+      <c r="W460" s="3"/>
+      <c r="X460" s="3"/>
+      <c r="Y460" s="3"/>
+    </row>
+    <row r="461" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C461" s="3"/>
       <c r="D461" s="3"/>
       <c r="E461" s="3"/>
@@ -11715,8 +13623,12 @@
       <c r="S461" s="3"/>
       <c r="T461" s="3"/>
       <c r="U461" s="3"/>
-    </row>
-    <row r="462" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V461" s="3"/>
+      <c r="W461" s="3"/>
+      <c r="X461" s="3"/>
+      <c r="Y461" s="3"/>
+    </row>
+    <row r="462" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C462" s="3"/>
       <c r="D462" s="3"/>
       <c r="E462" s="3"/>
@@ -11736,8 +13648,12 @@
       <c r="S462" s="3"/>
       <c r="T462" s="3"/>
       <c r="U462" s="3"/>
-    </row>
-    <row r="463" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V462" s="3"/>
+      <c r="W462" s="3"/>
+      <c r="X462" s="3"/>
+      <c r="Y462" s="3"/>
+    </row>
+    <row r="463" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C463" s="3"/>
       <c r="D463" s="3"/>
       <c r="E463" s="3"/>
@@ -11757,8 +13673,12 @@
       <c r="S463" s="3"/>
       <c r="T463" s="3"/>
       <c r="U463" s="3"/>
-    </row>
-    <row r="464" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V463" s="3"/>
+      <c r="W463" s="3"/>
+      <c r="X463" s="3"/>
+      <c r="Y463" s="3"/>
+    </row>
+    <row r="464" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C464" s="3"/>
       <c r="D464" s="3"/>
       <c r="E464" s="3"/>
@@ -11778,8 +13698,12 @@
       <c r="S464" s="3"/>
       <c r="T464" s="3"/>
       <c r="U464" s="3"/>
-    </row>
-    <row r="465" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V464" s="3"/>
+      <c r="W464" s="3"/>
+      <c r="X464" s="3"/>
+      <c r="Y464" s="3"/>
+    </row>
+    <row r="465" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C465" s="3"/>
       <c r="D465" s="3"/>
       <c r="E465" s="3"/>
@@ -11799,8 +13723,12 @@
       <c r="S465" s="3"/>
       <c r="T465" s="3"/>
       <c r="U465" s="3"/>
-    </row>
-    <row r="466" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V465" s="3"/>
+      <c r="W465" s="3"/>
+      <c r="X465" s="3"/>
+      <c r="Y465" s="3"/>
+    </row>
+    <row r="466" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C466" s="3"/>
       <c r="D466" s="3"/>
       <c r="E466" s="3"/>
@@ -11820,8 +13748,12 @@
       <c r="S466" s="3"/>
       <c r="T466" s="3"/>
       <c r="U466" s="3"/>
-    </row>
-    <row r="467" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V466" s="3"/>
+      <c r="W466" s="3"/>
+      <c r="X466" s="3"/>
+      <c r="Y466" s="3"/>
+    </row>
+    <row r="467" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C467" s="3"/>
       <c r="D467" s="3"/>
       <c r="E467" s="3"/>
@@ -11841,8 +13773,12 @@
       <c r="S467" s="3"/>
       <c r="T467" s="3"/>
       <c r="U467" s="3"/>
-    </row>
-    <row r="468" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V467" s="3"/>
+      <c r="W467" s="3"/>
+      <c r="X467" s="3"/>
+      <c r="Y467" s="3"/>
+    </row>
+    <row r="468" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C468" s="3"/>
       <c r="D468" s="3"/>
       <c r="E468" s="3"/>
@@ -11862,8 +13798,12 @@
       <c r="S468" s="3"/>
       <c r="T468" s="3"/>
       <c r="U468" s="3"/>
-    </row>
-    <row r="469" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V468" s="3"/>
+      <c r="W468" s="3"/>
+      <c r="X468" s="3"/>
+      <c r="Y468" s="3"/>
+    </row>
+    <row r="469" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C469" s="3"/>
       <c r="D469" s="3"/>
       <c r="E469" s="3"/>
@@ -11883,8 +13823,12 @@
       <c r="S469" s="3"/>
       <c r="T469" s="3"/>
       <c r="U469" s="3"/>
-    </row>
-    <row r="470" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V469" s="3"/>
+      <c r="W469" s="3"/>
+      <c r="X469" s="3"/>
+      <c r="Y469" s="3"/>
+    </row>
+    <row r="470" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C470" s="3"/>
       <c r="D470" s="3"/>
       <c r="E470" s="3"/>
@@ -11904,8 +13848,12 @@
       <c r="S470" s="3"/>
       <c r="T470" s="3"/>
       <c r="U470" s="3"/>
-    </row>
-    <row r="471" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V470" s="3"/>
+      <c r="W470" s="3"/>
+      <c r="X470" s="3"/>
+      <c r="Y470" s="3"/>
+    </row>
+    <row r="471" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C471" s="3"/>
       <c r="D471" s="3"/>
       <c r="E471" s="3"/>
@@ -11925,8 +13873,12 @@
       <c r="S471" s="3"/>
       <c r="T471" s="3"/>
       <c r="U471" s="3"/>
-    </row>
-    <row r="472" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V471" s="3"/>
+      <c r="W471" s="3"/>
+      <c r="X471" s="3"/>
+      <c r="Y471" s="3"/>
+    </row>
+    <row r="472" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C472" s="3"/>
       <c r="D472" s="3"/>
       <c r="E472" s="3"/>
@@ -11946,8 +13898,12 @@
       <c r="S472" s="3"/>
       <c r="T472" s="3"/>
       <c r="U472" s="3"/>
-    </row>
-    <row r="473" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V472" s="3"/>
+      <c r="W472" s="3"/>
+      <c r="X472" s="3"/>
+      <c r="Y472" s="3"/>
+    </row>
+    <row r="473" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C473" s="3"/>
       <c r="D473" s="3"/>
       <c r="E473" s="3"/>
@@ -11967,8 +13923,12 @@
       <c r="S473" s="3"/>
       <c r="T473" s="3"/>
       <c r="U473" s="3"/>
-    </row>
-    <row r="474" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V473" s="3"/>
+      <c r="W473" s="3"/>
+      <c r="X473" s="3"/>
+      <c r="Y473" s="3"/>
+    </row>
+    <row r="474" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C474" s="3"/>
       <c r="D474" s="3"/>
       <c r="E474" s="3"/>
@@ -11988,8 +13948,12 @@
       <c r="S474" s="3"/>
       <c r="T474" s="3"/>
       <c r="U474" s="3"/>
-    </row>
-    <row r="475" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V474" s="3"/>
+      <c r="W474" s="3"/>
+      <c r="X474" s="3"/>
+      <c r="Y474" s="3"/>
+    </row>
+    <row r="475" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C475" s="3"/>
       <c r="D475" s="3"/>
       <c r="E475" s="3"/>
@@ -12009,8 +13973,12 @@
       <c r="S475" s="3"/>
       <c r="T475" s="3"/>
       <c r="U475" s="3"/>
-    </row>
-    <row r="476" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V475" s="3"/>
+      <c r="W475" s="3"/>
+      <c r="X475" s="3"/>
+      <c r="Y475" s="3"/>
+    </row>
+    <row r="476" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C476" s="3"/>
       <c r="D476" s="3"/>
       <c r="E476" s="3"/>
@@ -12030,8 +13998,12 @@
       <c r="S476" s="3"/>
       <c r="T476" s="3"/>
       <c r="U476" s="3"/>
-    </row>
-    <row r="477" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V476" s="3"/>
+      <c r="W476" s="3"/>
+      <c r="X476" s="3"/>
+      <c r="Y476" s="3"/>
+    </row>
+    <row r="477" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C477" s="3"/>
       <c r="D477" s="3"/>
       <c r="E477" s="3"/>
@@ -12051,8 +14023,12 @@
       <c r="S477" s="3"/>
       <c r="T477" s="3"/>
       <c r="U477" s="3"/>
-    </row>
-    <row r="478" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V477" s="3"/>
+      <c r="W477" s="3"/>
+      <c r="X477" s="3"/>
+      <c r="Y477" s="3"/>
+    </row>
+    <row r="478" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C478" s="3"/>
       <c r="D478" s="3"/>
       <c r="E478" s="3"/>
@@ -12072,8 +14048,12 @@
       <c r="S478" s="3"/>
       <c r="T478" s="3"/>
       <c r="U478" s="3"/>
-    </row>
-    <row r="479" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V478" s="3"/>
+      <c r="W478" s="3"/>
+      <c r="X478" s="3"/>
+      <c r="Y478" s="3"/>
+    </row>
+    <row r="479" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C479" s="3"/>
       <c r="D479" s="3"/>
       <c r="E479" s="3"/>
@@ -12093,8 +14073,12 @@
       <c r="S479" s="3"/>
       <c r="T479" s="3"/>
       <c r="U479" s="3"/>
-    </row>
-    <row r="480" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V479" s="3"/>
+      <c r="W479" s="3"/>
+      <c r="X479" s="3"/>
+      <c r="Y479" s="3"/>
+    </row>
+    <row r="480" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C480" s="3"/>
       <c r="D480" s="3"/>
       <c r="E480" s="3"/>
@@ -12114,8 +14098,12 @@
       <c r="S480" s="3"/>
       <c r="T480" s="3"/>
       <c r="U480" s="3"/>
-    </row>
-    <row r="481" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V480" s="3"/>
+      <c r="W480" s="3"/>
+      <c r="X480" s="3"/>
+      <c r="Y480" s="3"/>
+    </row>
+    <row r="481" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C481" s="3"/>
       <c r="D481" s="3"/>
       <c r="E481" s="3"/>
@@ -12135,8 +14123,12 @@
       <c r="S481" s="3"/>
       <c r="T481" s="3"/>
       <c r="U481" s="3"/>
-    </row>
-    <row r="482" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V481" s="3"/>
+      <c r="W481" s="3"/>
+      <c r="X481" s="3"/>
+      <c r="Y481" s="3"/>
+    </row>
+    <row r="482" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C482" s="3"/>
       <c r="D482" s="3"/>
       <c r="E482" s="3"/>
@@ -12156,8 +14148,12 @@
       <c r="S482" s="3"/>
       <c r="T482" s="3"/>
       <c r="U482" s="3"/>
-    </row>
-    <row r="483" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V482" s="3"/>
+      <c r="W482" s="3"/>
+      <c r="X482" s="3"/>
+      <c r="Y482" s="3"/>
+    </row>
+    <row r="483" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C483" s="3"/>
       <c r="D483" s="3"/>
       <c r="E483" s="3"/>
@@ -12177,8 +14173,12 @@
       <c r="S483" s="3"/>
       <c r="T483" s="3"/>
       <c r="U483" s="3"/>
-    </row>
-    <row r="484" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V483" s="3"/>
+      <c r="W483" s="3"/>
+      <c r="X483" s="3"/>
+      <c r="Y483" s="3"/>
+    </row>
+    <row r="484" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C484" s="3"/>
       <c r="D484" s="3"/>
       <c r="E484" s="3"/>
@@ -12198,8 +14198,12 @@
       <c r="S484" s="3"/>
       <c r="T484" s="3"/>
       <c r="U484" s="3"/>
-    </row>
-    <row r="485" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V484" s="3"/>
+      <c r="W484" s="3"/>
+      <c r="X484" s="3"/>
+      <c r="Y484" s="3"/>
+    </row>
+    <row r="485" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C485" s="3"/>
       <c r="D485" s="3"/>
       <c r="E485" s="3"/>
@@ -12219,8 +14223,12 @@
       <c r="S485" s="3"/>
       <c r="T485" s="3"/>
       <c r="U485" s="3"/>
-    </row>
-    <row r="486" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V485" s="3"/>
+      <c r="W485" s="3"/>
+      <c r="X485" s="3"/>
+      <c r="Y485" s="3"/>
+    </row>
+    <row r="486" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C486" s="3"/>
       <c r="D486" s="3"/>
       <c r="E486" s="3"/>
@@ -12240,6 +14248,10 @@
       <c r="S486" s="3"/>
       <c r="T486" s="3"/>
       <c r="U486" s="3"/>
+      <c r="V486" s="3"/>
+      <c r="W486" s="3"/>
+      <c r="X486" s="3"/>
+      <c r="Y486" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
